--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +55,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C62828"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -69,7 +73,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -114,6 +118,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+        <bgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
@@ -137,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,21 +176,24 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -551,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -653,7 +666,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>জারুন</t>
+          <t>ধর্ষণ</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -663,7 +676,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, abuse</t>
+          <t>assault, attack</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -703,7 +716,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>মুরদ্ত</t>
+          <t>হত্যা</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -723,7 +736,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>The murder took place in the middle of the night.</t>
+          <t>The murder took place in a dark alley.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -753,7 +766,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>পুনরনোনেথে</t>
+          <t>পুনর্নবীকরণযোগ্য</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -768,12 +781,12 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, unsustainable</t>
+          <t>non-renewable, exhaustible</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Renewable energy sources are becoming more popular.</t>
+          <t>Renewable energy sources are becoming increasingly popular.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -803,7 +816,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>কেনদুল</t>
+          <t>ঘোরানো</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -823,7 +836,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The company will pivot to a new business model.</t>
+          <t>The company will pivot to a new business strategy.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -853,12 +866,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u09acেলে</t>
+          <t>বিস্মৃত</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>not remembered or thought about</t>
+          <t>no longer remembered or considered</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -903,7 +916,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>আতেন্দ</t>
+          <t>বৃদ্ধি</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -923,12 +936,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The country is experiencing a boom in the tech industry.</t>
+          <t>India's economy is experiencing a boom.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -938,7 +951,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -946,39 +959,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u09aaদুল</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>goods or products that can be bought and sold</t>
+          <t>a piece of advice or guidance</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>goods, products</t>
+          <t>advice, guidance</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>services, experiences</t>
+          <t>ignorance, mistake</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The price of commodities is increasing.</t>
+          <t>The lesson learned from the experience was valuable.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>education</t>
         </is>
       </c>
     </row>
@@ -988,12 +1001,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>diary</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1003,32 +1016,32 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>ঔেরে</t>
+          <t>ডায়েরি</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>more expensive</t>
+          <t>a book in which you write down your thoughts and feelings</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>more expensive, costlier</t>
+          <t>journal, log</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>cheaper, less expensive</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The commodities are becoming dearer.</t>
+          <t>She kept a diary throughout her trip.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>personal</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1051,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>historian</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1046,39 +1059,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>আকুল \u0995রন</t>
+          <t>ঐতিহাসিক</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>an activity done to prepare for a game or exercise</t>
+          <t>a person who studies and writes about history</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>practice, preparation</t>
+          <t>scholar, researcher</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>game, match</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team played a warm-up match before the tournament.</t>
+          <t>The historian spent years researching the topic.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -1088,47 +1101,47 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>guide</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>আকুল \u0995রন</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>to show or lead someone to a place or goal</t>
+          <t>goods or products that are bought and sold</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>lead, direct</t>
+          <t>goods, products</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>follow, obey</t>
+          <t>services</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The coach will guide the team to victory.</t>
+          <t>The price of commodities is increasing.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1151,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1153,32 +1166,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>কেনদুল</t>
+          <t>দামি</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>the middle or central part of something</t>
+          <t>more expensive</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>middle, central</t>
+          <t>expensive, costly</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>edge, periphery</t>
+          <t>cheap, affordable</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The player took centre stage in the match.</t>
+          <t>The commodities are becoming dearer.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1201,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>guide</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1203,27 +1216,27 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>কসেনদুল</t>
+          <t>পথ দেখানো</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a particular point or period in a process or development</t>
+          <t>to show or lead someone to a place</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>level, phase</t>
+          <t>lead, direct</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>beginning, end</t>
+          <t>mislead, confuse</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The team is at the final stage of the tournament.</t>
+          <t>The coach will guide the team to victory.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1238,42 +1251,42 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Copa</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>কোপা</t>
+          <t>উষ্ণতা বাড়ানো</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>a international football tournament</t>
+          <t>an exercise or activity done before a main event</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>tournament, championship</t>
+          <t>preparation, practice</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>friendly, exhibition</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The team won the Copa America.</t>
+          <t>The team did a warm-up before the match.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1288,7 +1301,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1296,34 +1309,34 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>কসেনে \u0995লে</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>the state of continuing to live or exist</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>existence, life</t>
+          <t>middle, central</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>edge, periphery</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The team is fighting for survival in the tournament.</t>
+          <t>The player took centre stage.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1338,42 +1351,42 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>maiden</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>কুমেলে</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>first or initial</t>
+          <t>a particular point or period in a process</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>first, initial</t>
+          <t>level, phase</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>last, final</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The team is seeking their maiden win in the tournament.</t>
+          <t>The team is at the final stage of the competition.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1388,12 +1401,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>mighty</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1403,27 +1416,27 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>খোরে</t>
+          <t>বেঁচে থাকা</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>very strong or powerful</t>
+          <t>the state of continuing to live or exist</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>powerful, strong</t>
+          <t>existence, life</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>weak, powerless</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The team is facing a mighty opponent in the next match.</t>
+          <t>The team is fighting for survival.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -1438,47 +1451,47 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>maiden</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>এন্যলেনদ</t>
+          <t>প্রথম</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>a country in Northwest Europe</t>
+          <t>first or initial</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>UK, Britain</t>
+          <t>first, initial</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>second, subsequent</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The team is playing against England in the next match.</t>
+          <t>The team is seeking their maiden win.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1501,47 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>iran</t>
+          <t>mighty</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>proper noun</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>এরান</t>
+          <t>শক্তিশালী</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>a country in the Middle East</t>
+          <t>very strong or powerful</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Persia</t>
+          <t>strong, powerful</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>weak, powerless</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>The historian is studying the Iran war.</t>
+          <t>The team is facing a mighty opponent.</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1551,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>doha</t>
+          <t>england</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1546,24 +1559,24 @@
           <t>proper noun</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>দোহা</t>
+          <t>ইংল্যান্ড</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>the capital city of Qatar</t>
+          <t>a country in Northwest Europe</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1573,7 +1586,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>The historian is writing a diary from Doha.</t>
+          <t>The team is playing against England.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1588,12 +1601,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>diary</t>
+          <t>search</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1603,32 +1616,32 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>দেনে \u0995সেনে</t>
+          <t>অনুসন্ধান করা</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>a book in which you write down your thoughts and feelings</t>
+          <t>to look for something</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>journal, log</t>
+          <t>look, seek</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>find, discover</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>The historian is keeping a diary of his experiences.</t>
+          <t>The team is searching for a win.</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1638,47 +1651,47 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>historian</t>
+          <t>win</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>এতেহাসে</t>
+          <t>জয় লাভ করা</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>a person who studies and writes about history</t>
+          <t>to achieve a victory or success</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>scholar, researcher</t>
+          <t>achieve, succeed</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>lose, fail</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>The historian is studying the Iran war.</t>
+          <t>The team won the match.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1701,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1696,24 +1709,24 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>খরেশ্থ</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>the creation and expression of beautiful or thought-provoking works</t>
+          <t>a formal accusation or allegation</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>creation, expression</t>
+          <t>allegation, accusation</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1723,12 +1736,12 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>The forgotten art of Bengali advertising is being revived.</t>
+          <t>The charges against the defendant were dropped.</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1751,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1753,32 +1766,32 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u09aaরনে</t>
+          <t>তৈরি করা</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>the activity of promoting a product or service</t>
+          <t>to create or construct something</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>promotion, marketing</t>
+          <t>create, construct</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>destroy, demolish</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>The forgotten art of Bengali advertising is being revived.</t>
+          <t>The charges were framed against the defendant.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1801,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>bengali</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1803,17 +1816,17 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>জলে</t>
+          <t>নাম</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>relating to Bangladesh or the Bengali language</t>
+          <t>a word or phrase that identifies someone or something</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Bangladeshi</t>
+          <t>title, label</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1823,12 +1836,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>The forgotten art of Bengali advertising is being revived.</t>
+          <t>The defendant's name was mentioned in the charges.</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1851,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1853,32 +1866,32 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u09aaান</t>
+          <t>শক্তি</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>a piece of advice or guidance</t>
+          <t>the ability or strength to do something</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>advice, guidance</t>
+          <t>power, strength</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>weakness, fatigue</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>The country can learn a lesson from India's economic boom.</t>
+          <t>The team has a lot of energy.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1888,47 +1901,47 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>এত \u0995সেনে</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>the creation of beautiful or imaginative works</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>creation, imagination</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>balanced, even</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>The country's economy is top-heavy, with too much reliance on one industry.</t>
+          <t>The art of Bengali advertising is being revived.</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1951,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1946,39 +1959,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>আতেন্দ</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>a period of rapid economic growth</t>
+          <t>the act of promoting or publicizing something</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>expansion, growth</t>
+          <t>promotion, publicity</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>recession, decline</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>The country is experiencing a boom in the tech industry.</t>
+          <t>The art of Bengali advertising is being revived.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1988,47 +2001,47 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>কসেনে \u0995রন</t>
+          <t>বৃদ্ধি পাওয়া</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>a formal accusation of a crime</t>
+          <t>to increase or expand rapidly</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>accusation, allegation</t>
+          <t>expand, grow</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>decline, shrink</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>The suspect is facing charges of murder.</t>
+          <t>The economy is booming.</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>crime</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -2038,47 +2051,47 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u0995রন</t>
+          <t>ওপরের দিকে ভারী</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>to accuse someone of a crime</t>
+          <t>having a large or excessive amount of something at the top</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>accuse, charge</t>
+          <t>unbalanced, unstable</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>clear, exonerate</t>
+          <t>balanced, stable</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>The suspect was framed for the crime.</t>
+          <t>The top-heavy economy is at risk of collapse.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>crime</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2101,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -2103,32 +2116,32 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>কসেনে</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>a word or phrase that identifies someone or something</t>
+          <t>a piece of advice or guidance</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>title, label</t>
+          <t>advice, guidance</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ignorance, mistake</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>The suspect mentioned a new name in the investigation.</t>
+          <t>The lesson learned from the experience was valuable.</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>education</t>
         </is>
       </c>
     </row>
@@ -2138,47 +2151,47 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>sustainable</t>
+          <t>iran</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u0995রন</t>
+          <t>ইরান</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>able to be maintained or supported without harm to the environment</t>
+          <t>a country in the Middle East</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>eco-friendly, renewable</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>unsustainable, harmful</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>The company is committed to sustainable practices.</t>
+          <t>The historian is an expert on Iran.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -2188,47 +2201,47 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>eco-friendly</t>
+          <t>war</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>কসেনে \u0995রন</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>not harming the environment</t>
+          <t>a state of armed conflict between nations or groups</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>sustainable, renewable</t>
+          <t>conflict, battle</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>harmful, polluting</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>The company is using eco-friendly packaging.</t>
+          <t>The war in Iran is ongoing.</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>politics</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2251,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>doha</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>proper noun</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2253,17 +2266,17 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>কসেনে \u0995রন</t>
+          <t>দোহা</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>the natural world around us</t>
+          <t>the capital city of Qatar</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>nature, ecosystem</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2273,12 +2286,12 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>The company is committed to protecting the environment.</t>
+          <t>The historian is in Doha.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2301,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>diary</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -2303,17 +2316,17 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>কসেনে করন</t>
+          <t>ডায়েরি</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>the decade from 1950 to 1959</t>
+          <t>a book in which you write down your thoughts and feelings</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>fifty, half-century</t>
+          <t>journal, log</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2323,12 +2336,12 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>The player scored two fifties in the match.</t>
+          <t>The historian kept a diary in Doha.</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>personal</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2351,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>tigers</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2346,39 +2359,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>জলে</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>a large cat native to Asia</t>
+          <t>goods or products that are bought and sold</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>big cat, predator</t>
+          <t>goods, products</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>services</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>The Bangladesh cricket team is known as the Tigers.</t>
+          <t>The price of commodities is increasing.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2401,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -2403,32 +2416,32 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>জেন</t>
+          <t>চালিয়ে যাওয়া</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>to achieve a victory or success</t>
+          <t>to keep doing something</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>achieve, succeed</t>
+          <t>keep, persist</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>lose, fail</t>
+          <t>stop, cease</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>The team won the match.</t>
+          <t>The commodities market will continue to fluctuate.</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2451,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>brazil</t>
+          <t>tigers</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2453,12 +2466,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>জরাসল</t>
+          <t>বাঘ</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>a country in South America</t>
+          <t>a large wild cat</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2473,12 +2486,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Brazil won the Copa America.</t>
+          <t>The tigers are playing in the warm-up match.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -2488,52 +2501,402 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
+          <t>warm-up</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>উষ্ণতা বাড়ানো</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>an exercise or activity done before a main event</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>preparation, practice</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>The tigers are doing a warm-up before the match.</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>jesus</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>proper noun</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>জেসু</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>a central figure in Christianity</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Christ, Messiah</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>যীশু</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>the central figure of Christianity</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Jesus is a popular name in Brazil.</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Jesus is a significant figure in Christianity.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
     </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>brazil</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>ব্রাজিল</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>a country in South America</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Brazil won the Copa America.</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>copa</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>কোপা</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>a international football tournament</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Brazil won the Copa America.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>america</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>আমেরিকা</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>a continent in the Western Hemisphere</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Brazil won the Copa America.</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>south</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>দক্ষিণ</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>located in the southern part of a region</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>southern, southernmost</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>north, northern</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>South Africa is a country in Africa.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>africa</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>আফ্রিকা</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>a continent in the Eastern Hemisphere</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>South Africa is a country in Africa.</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>pakistan</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>পাকিস্তান</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>a country in South Asia</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan is playing in the tournament.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J42"/>
+  <autoFilter ref="A4:J49"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -2552,19 +2915,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>DAILY STAR VOCABULARY ANALYSIS - BCS &amp; JOB EXAM FOCUS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>VOCABULARY BREAKDOWN BY LEVEL</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>VOCABULARY DISTRIBUTION BY NEWSPAPER SECTOR</t>
         </is>
@@ -2609,10 +2972,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0.6052631578947368</v>
+        <v>30</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -2622,10 +2985,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0.3947368421052632</v>
+        <v>14</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.3111111111111111</v>
       </c>
     </row>
     <row r="7">
@@ -2635,10 +2998,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="8">
@@ -2657,35 +3020,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>BANGLADESHI JOB EXAM PREPARATION GUIDELINES (BCS, BANK, NTRCA, PRIMARY)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>1. BCS Preliminary Strategy: Daily Star editorials contain high-frequency synonyms/antonyms asked directly in BCS Preliminary (20 Marks English). Focus on Advanced words.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>2. BCS Written Strategy: Words like 'Rupture', 'Reimagine', 'Transboundary', 'Exacerbate' enhance the standard of translation and passage writing in BCS Written.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>3. Bank Recruitment Exams: Bank exams heavily emphasize vocabulary in context, reading comprehension, and fill-in-the-blanks. Learn synonyms and precise nuances.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>4. Revision Technique: Practice making sentences using 5 new Daily Star vocabulary words daily to retain Bengali meaning and appropriate usage.</t>
         </is>
@@ -2719,403 +3082,403 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>DAILY STAR VOCABULARY PRACTICE SET (JOB EXAM MODEL TEST)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Test your vocabulary knowledge for upcoming BCS Preliminary, Combined Bank Officers, and Primary Teacher exams.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Q. No</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Question / Contextual Sentence</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Correct Answer &amp; Explanation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Which country is often associated with the historian's research on medieval times?</t>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>What is a 'maiden' voyage?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>A first trip by car</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>A first trip by ship</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A first trip by plane</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A first trip by train</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>B — A 'maiden' voyage refers to the first trip or journey of a ship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Which country is known for its Carnival celebrations?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>America</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>B — England is often associated with medieval history, given its rich historical heritage and numerous medieval sites.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>What is a diary typically used for?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Recording historical events</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Writing letters to friends</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Documenting daily personal experiences</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conducting scientific research</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>C — A diary is a personal record of an individual's daily experiences, thoughts, and feelings.</t>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>C — Brazil is famous for its vibrant Carnival celebrations.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Which of the following animals is known for its distinctive stripes?</t>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>What does 'top-heavy' mean?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lions</t>
+          <t>Having more weight at the bottom</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bears</t>
+          <t>Having more weight at the top</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tigers</t>
+          <t>Having equal weight throughout</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wolves</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>C — Tigers are known for their distinctive orange and black stripes, which act as camouflage in their natural habitats.</t>
+          <t>Having no weight at all</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>B — 'Top-heavy' refers to something that has more weight or emphasis at the top.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
+      <c r="A8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>What does the term 'pivot' mean in a business context?</t>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>What is 'art'?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>To stay the same</t>
+          <t>A type of science</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To change direction</t>
+          <t>A type of music</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>To increase production</t>
+          <t>A type of creative expression</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>To decrease staff</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>B — In a business context, to pivot means to change direction or strategy, often in response to changes in the market or industry.</t>
+          <t>A type of sport</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>C — 'Art' refers to a wide range of creative expressions, including painting, sculpture, and music.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>What does the phrase 'dearer than' mean?</t>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>What does it mean to 'win' something?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>More expensive than</t>
+          <t>To lose something</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Less expensive than</t>
+          <t>To gain something</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Equally expensive as</t>
+          <t>To forget something</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Completely free</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>A — The phrase 'dearer than' means more expensive than something else, often used to compare prices or costs.</t>
+          <t>To give up something</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>B — To 'win' something means to gain or achieve it, often through competition or effort.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>What is the primary goal of competing in a sporting event?</t>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Which country is known for its love of tea and cricket?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>To lose</t>
+          <t>America</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To draw</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>To have fun</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>To win</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>D — The primary goal of competing in a sporting event is often to win, although having fun and improving skills are also important aspects.</t>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>C — England is famous for its love of tea and cricket.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Which decade is often associated with the rise of rock and roll music?</t>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>What does 'forgotten' mean?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Forties</t>
+          <t>Remembered clearly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fifties</t>
+          <t>Not remembered at all</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sixties</t>
+          <t>Partially remembered</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seventies</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>B — The fifties are often associated with the rise of rock and roll music, with artists like Elvis Presley and Chuck Berry gaining popularity during this time.</t>
+          <t>Not important</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>B — 'Forgotten' means not remembered or no longer kept in mind.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>What is the role of a guide in a museum?</t>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>What is a 'warm-up'?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>To clean the exhibits</t>
+          <t>A cool-down exercise</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To manage the staff</t>
+          <t>A stretching exercise</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>To provide information to visitors</t>
+          <t>An exercise to prepare for physical activity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>To handle the finances</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>C — A guide in a museum is responsible for providing information and explanations to visitors about the exhibits and collections on display.</t>
+          <t>A type of sport</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>C — A 'warm-up' is an exercise or activity done to prepare the body for physical activity or sport.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>What are charges in a legal context?</t>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>What is a 'diary'?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fees for a service</t>
+          <t>A type of book for writing notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Penalties for a crime</t>
+          <t>A type of book for writing stories</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Taxes on income</t>
+          <t>A personal record of daily events and thoughts</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>All of the above</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>D — In a legal context, charges can refer to fees for a service, penalties for a crime, or taxes on income, depending on the specific situation.</t>
+          <t>A type of calendar</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>C — A 'diary' is a personal record of daily events, thoughts, and feelings, often written in a book or digital format.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n">
+      <c r="A14" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Which of the following is an example of a historical figure who might be studied by a historian?</t>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Which of the following countries is often referred to as a 'melting pot' of cultures?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A modern-day athlete</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A fictional character</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A medieval king</t>
+          <t>America</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A scientist from the future</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>C — A historian would typically study historical figures from the past, such as a medieval king, to understand their role in shaping historical events and societies.</t>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>C — America is often referred to as a 'melting pot' of cultures due to its diverse population and history of immigration.</t>
         </is>
       </c>
     </row>

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,10 +55,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C62828"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -73,7 +69,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -118,12 +114,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
-        <bgColor rgb="00FFEBEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
@@ -147,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,24 +166,21 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -564,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -676,12 +663,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, attack</t>
+          <t>assault, abuse, violation</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, agreement</t>
+          <t>consent, permission, agreement</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -726,17 +713,17 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>killing, homicide</t>
+          <t>killing, homicide, slaughter</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>life, survival</t>
+          <t>life, survival, preservation</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>The murder took place in a dark alley.</t>
+          <t>The murder took place in a deserted alley.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -776,12 +763,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly</t>
+          <t>sustainable, eco-friendly, green</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, exhaustible</t>
+          <t>non-renewable, exhaustible, finite</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -826,17 +813,17 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>turn, shift</t>
+          <t>shift, turn, change</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>stay, remain</t>
+          <t>remain, stay, continue</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The company will pivot to a new business strategy.</t>
+          <t>The company will pivot to a new business model.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -876,12 +863,12 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>overlooked, neglected</t>
+          <t>neglected, overlooked, ignored</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>remembered, recalled</t>
+          <t>remembered, recalled, recognized</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -926,22 +913,22 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>expansion, growth</t>
+          <t>expansion, growth, prosperity</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>recession, decline</t>
+          <t>recession, decline, slump</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>India's economy is experiencing a boom.</t>
+          <t>India is experiencing a top-heavy boom.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -951,7 +938,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -959,39 +946,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>a piece of advice or guidance</t>
+          <t>goods or products that can be bought or sold</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>advice, guidance</t>
+          <t>goods, products, merchandise</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>ignorance, mistake</t>
+          <t>services, intangibles, non-physical goods</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The lesson learned from the experience was valuable.</t>
+          <t>Commodities continue to be dearer in the market.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -1001,7 +988,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>diary</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1016,32 +1003,32 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>ডায়েরি</t>
+          <t>উষ্ণতা বৃদ্ধি</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a book in which you write down your thoughts and feelings</t>
+          <t>an activity done to prepare for a game or exercise</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>journal, log</t>
+          <t>practice, preparation, rehearsal</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>cool-down, relaxation, rest</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>She kept a diary throughout her trip.</t>
+          <t>The team played a warm-up match before the tournament.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1038,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>historian</t>
+          <t>Copa</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>proper noun</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1066,32 +1053,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ঐতিহাসিক</t>
+          <t>কোপা</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a person who studies and writes about history</t>
+          <t>a international football tournament</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>scholar, researcher</t>
+          <t>tournament, championship, league</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>friendly, exhibition, non-competitive match</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The historian spent years researching the topic.</t>
+          <t>Brazil won the Copa America.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1088,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1109,39 +1096,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>বেঁচে থাকা</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>the state of continuing to live or exist</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>goods, products</t>
+          <t>existence, life, subsistence</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>death, extinction, annihilation</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities is increasing.</t>
+          <t>The team is fighting for survival in the tournament.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1138,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>maiden</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1159,39 +1146,39 @@
           <t>adjective</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>দামি</t>
+          <t>প্রথম</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>more expensive</t>
+          <t>first or initial</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>expensive, costly</t>
+          <t>first, initial, debut</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>cheap, affordable</t>
+          <t>second, subsequent, experienced</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The commodities are becoming dearer.</t>
+          <t>The Afghans are searching for their maiden win.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1188,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>guide</t>
+          <t>mighty</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1216,27 +1203,27 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>পথ দেখানো</t>
+          <t>শক্তিশালী</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>to show or lead someone to a place</t>
+          <t>very strong or powerful</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>lead, direct</t>
+          <t>strong, powerful, potent</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>mislead, confuse</t>
+          <t>weak, feeble, powerless</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The coach will guide the team to victory.</t>
+          <t>England is a mighty team in the tournament.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1251,7 +1238,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1266,32 +1253,32 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>উষ্ণতা বাড়ানো</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>an exercise or activity done before a main event</t>
+          <t>the expression or application of human creative skill</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>preparation, practice</t>
+          <t>craft, skill, creativity</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>science, technology, engineering</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The team did a warm-up before the match.</t>
+          <t>The art of Bengali advertising is being revived.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1288,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1316,32 +1303,32 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>the middle or central part of something</t>
+          <t>the activity of promoting a product or service</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>middle, central</t>
+          <t>promotion, marketing, publicity</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>edge, periphery</t>
+          <t>concealment, secrecy, silence</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The player took centre stage.</t>
+          <t>The art of Bengali advertising is being revived.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1338,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>diary</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1366,32 +1353,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>ডায়েরি</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>a particular point or period in a process</t>
+          <t>a book in which you write down your thoughts or events</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>level, phase</t>
+          <t>journal, log, record</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>fiction, novel, story</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The team is at the final stage of the competition.</t>
+          <t>The historian kept a diary during the Iran war.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>literature</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1388,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>historian</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1416,32 +1403,32 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>বেঁচে থাকা</t>
+          <t>ঐতিহাসিক</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>the state of continuing to live or exist</t>
+          <t>a person who studies and writes about history</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>existence, life</t>
+          <t>scholar, researcher, expert</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>amateur, novice, non-expert</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The team is fighting for survival.</t>
+          <t>The historian kept a diary during the Iran war.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -1451,47 +1438,47 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>maiden</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>প্রথম</t>
+          <t>ইরান</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>first or initial</t>
+          <t>a country in the Middle East</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>first, initial</t>
+          <t>Persia, Islamic Republic of Iran</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>second, subsequent</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The team is seeking their maiden win.</t>
+          <t>The historian kept a diary during the Iran war.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -1501,47 +1488,47 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>mighty</t>
+          <t>war</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>শক্তিশালী</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>very strong or powerful</t>
+          <t>a state of armed conflict between different nations or states</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>strong, powerful</t>
+          <t>conflict, battle, fight</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>weak, powerless</t>
+          <t>peace, harmony, tranquility</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>The team is facing a mighty opponent.</t>
+          <t>The historian kept a diary during the Iran war.</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1538,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1566,32 +1553,32 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>ইংল্যান্ড</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>a country in Northwest Europe</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>middle, central, middle point</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>periphery, edge, border</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>The team is playing against England.</t>
+          <t>Jesus took centre stage as Brazil won the Copa America.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1588,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1616,27 +1603,27 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>অনুসন্ধান করা</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>to look for something</t>
+          <t>a particular point or period in a process or development</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>look, seek</t>
+          <t>level, phase, period</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>find, discover</t>
+          <t>beginning, end, completion</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>The team is searching for a win.</t>
+          <t>Jesus took centre stage as Brazil won the Copa America.</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -1651,12 +1638,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>proper noun</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1666,32 +1653,32 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>জয় লাভ করা</t>
+          <t>ব্রাজিল</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>to achieve a victory or success</t>
+          <t>a country in South America</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>achieve, succeed</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>lose, fail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>The team won the match.</t>
+          <t>Jesus took centre stage as Brazil won the Copa America.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1688,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>Copa America</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>proper noun</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -1716,32 +1703,32 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>কোপা আমেরিকা</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>a formal accusation or allegation</t>
+          <t>a international football tournament</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>allegation, accusation</t>
+          <t>tournament, championship, league</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>friendly, exhibition, non-competitive match</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>The charges against the defendant were dropped.</t>
+          <t>Jesus took centre stage as Brazil won the Copa America.</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1751,47 +1738,47 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>তৈরি করা</t>
+          <t>ইংল্যান্ড</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>to create or construct something</t>
+          <t>a country in Northwest Europe</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>create, construct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>destroy, demolish</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>The charges were framed against the defendant.</t>
+          <t>The Afghans are searching for their maiden win against England.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1788,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Afghans</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1816,17 +1803,17 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>নাম</t>
+          <t>আফগান</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>a word or phrase that identifies someone or something</t>
+          <t>people from Afghanistan</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>title, label</t>
+          <t>Afghan people, Afghan nation</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1836,12 +1823,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>The defendant's name was mentioned in the charges.</t>
+          <t>The Afghans are searching for their maiden win against England.</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>people</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1838,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>searching</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1866,32 +1853,32 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>শক্তি</t>
+          <t>অনুসন্ধান</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>the ability or strength to do something</t>
+          <t>looking or trying to find something</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>power, strength</t>
+          <t>looking, seeking, trying</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>weakness, fatigue</t>
+          <t>finding, discovering, locating</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>The team has a lot of energy.</t>
+          <t>The Afghans are searching for their maiden win against England.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -1901,47 +1888,47 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>দামি</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>the creation of beautiful or imaginative works</t>
+          <t>more expensive or costly</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>creation, imagination</t>
+          <t>expensive, costly, pricey</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>cheaper, affordable, inexpensive</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>The art of Bengali advertising is being revived.</t>
+          <t>Commodities continue to be dearer in the market.</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1938,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1959,24 +1946,24 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>পঞ্চাশের দশক</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>the act of promoting or publicizing something</t>
+          <t>a score of 50 or more in cricket</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>promotion, publicity</t>
+          <t>half-century, fifty</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -1986,12 +1973,12 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>The art of Bengali advertising is being revived.</t>
+          <t>Mithun and Mushfiqur scored fifties to guide Tigers to win in warm-up.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -2001,7 +1988,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>guide</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -2009,39 +1996,39 @@
           <t>verb</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>বৃদ্ধি পাওয়া</t>
+          <t>পথ দেখানো</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>to increase or expand rapidly</t>
+          <t>to show or lead someone to a place or destination</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>expand, grow</t>
+          <t>lead, direct, show</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>decline, shrink</t>
+          <t>mislead, misdirect, confuse</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>The economy is booming.</t>
+          <t>Mithun and Mushfiqur scored fifties to guide Tigers to win in warm-up.</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -2051,47 +2038,47 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>ওপরের দিকে ভারী</t>
+          <t>উষ্ণতা বৃদ্ধি</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>having a large or excessive amount of something at the top</t>
+          <t>an activity done to prepare for a game or exercise</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, unstable</t>
+          <t>practice, preparation, rehearsal</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>balanced, stable</t>
+          <t>cool-down, relaxation, rest</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>The top-heavy economy is at risk of collapse.</t>
+          <t>Mithun and Mushfiqur scored fifties to guide Tigers to win in warm-up.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2088,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>Tigers</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -2116,32 +2103,32 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>বাঘ</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>a piece of advice or guidance</t>
+          <t>the national cricket team of Bangladesh</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>advice, guidance</t>
+          <t>Bangladesh cricket team</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ignorance, mistake</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>The lesson learned from the experience was valuable.</t>
+          <t>Mithun and Mushfiqur scored fifties to guide Tigers to win in warm-up.</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2138,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>iran</t>
+          <t>win</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2166,32 +2153,32 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>ইরান</t>
+          <t>জয়</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>a country in the Middle East</t>
+          <t>to achieve a victory or success</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>victory, success, triumph</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>loss, defeat, failure</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>The historian is an expert on Iran.</t>
+          <t>Mithun and Mushfiqur scored fifties to guide Tigers to win in warm-up.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2188,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>war</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -2216,32 +2203,32 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>a state of armed conflict between nations or groups</t>
+          <t>a formal accusation or allegation</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>conflict, battle</t>
+          <t>accusation, allegation, indictment</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony</t>
+          <t>acquittal, dismissal, exoneration</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>The war in Iran is ongoing.</t>
+          <t>Sohel Rana mentions new name as charges framed.</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>politics</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2238,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>doha</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2266,32 +2253,32 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>দোহা</t>
+          <t>গঠন করা</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>the capital city of Qatar</t>
+          <t>to create or establish something</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>create, establish, set up</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>destroy, dismantle, abolish</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>The historian is in Doha.</t>
+          <t>Sohel Rana mentions new name as charges framed.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2288,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>diary</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -2316,32 +2303,32 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>ডায়েরি</t>
+          <t>নাম</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>a book in which you write down your thoughts and feelings</t>
+          <t>a word or phrase that identifies someone or something</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>journal, log</t>
+          <t>title, label, designation</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>anonymous, unnamed, unidentified</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>The historian kept a diary in Doha.</t>
+          <t>Sohel Rana mentions new name as charges framed.</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>identification</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2338,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2359,39 +2346,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>a piece of advice or instruction</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>goods, products</t>
+          <t>advice, instruction, guidance</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>ignorance, unawareness, misunderstanding</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>The price of commodities is increasing.</t>
+          <t>India’s top-heavy boom and the lesson for Bangladesh.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>education</t>
         </is>
       </c>
     </row>
@@ -2401,47 +2388,47 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>চালিয়ে যাওয়া</t>
+          <t>উপরিভারী</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>to keep doing something</t>
+          <t>having a large or excessive amount at the top</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>keep, persist</t>
+          <t>unbalanced, uneven, lopsided</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>stop, cease</t>
+          <t>balanced, even, symmetrical</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>The commodities market will continue to fluctuate.</t>
+          <t>India’s top-heavy boom and the lesson for Bangladesh.</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2438,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>tigers</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2459,39 +2446,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>বাঘ</t>
+          <t>বৃদ্ধি</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>a large wild cat</t>
+          <t>a period of rapid economic growth</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>expansion, growth, prosperity</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>recession, decline, slump</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>The tigers are playing in the warm-up match.</t>
+          <t>India’s top-heavy boom and the lesson for Bangladesh.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2488,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>proper noun</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -2516,17 +2503,17 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>উষ্ণতা বাড়ানো</t>
+          <t>দোহা</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>an exercise or activity done before a main event</t>
+          <t>the capital city of Qatar</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>preparation, practice</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2536,12 +2523,12 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>The tigers are doing a warm-up before the match.</t>
+          <t>Doha diary: A historian amid the Iran war.</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2538,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>jesus</t>
+          <t>diary</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -2566,32 +2553,32 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>যীশু</t>
+          <t>ডায়েরি</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>the central figure of Christianity</t>
+          <t>a book in which you write down your thoughts or events</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>journal, log, record</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>fiction, novel, story</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Jesus is a significant figure in Christianity.</t>
+          <t>Doha diary: A historian amid the Iran war.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>religion</t>
+          <t>literature</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2588,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>brazil</t>
+          <t>amid</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>preposition</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -2616,32 +2603,32 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>ব্রাজিল</t>
+          <t>মধ্যে</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>a country in South America</t>
+          <t>in the middle of or surrounded by</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>among, amongst, surrounded</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>outside, apart, separate</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Brazil won the Copa America.</t>
+          <t>Doha diary: A historian amid the Iran war.</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>location</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2638,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>copa</t>
+          <t>Jesus</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2666,32 +2653,32 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>কোপা</t>
+          <t>যীশু</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>a international football tournament</t>
+          <t>a major figure in Christianity</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>Christ, Messiah, Savior</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Brazil won the Copa America.</t>
+          <t>Jesus takes centre stage as Brazil win Copa America.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>religion</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2688,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>america</t>
+          <t>takes</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -2716,32 +2703,32 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>আমেরিকা</t>
+          <t>নেয়</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>a continent in the Western Hemisphere</t>
+          <t>to get or obtain something</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>get, obtain, acquire</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>give, lose, surrender</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Brazil won the Copa America.</t>
+          <t>Jesus takes centre stage as Brazil win Copa America.</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>action</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2738,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>south</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -2766,32 +2753,32 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>দক্ষিণ</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>located in the southern part of a region</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>southern, southernmost</t>
+          <t>middle, central, middle point</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>north, northern</t>
+          <t>periphery, edge, border</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>South Africa is a country in Africa.</t>
+          <t>Jesus takes centre stage as Brazil win Copa America.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>location</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2788,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>africa</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -2816,32 +2803,32 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>আফ্রিকা</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>a continent in the Eastern Hemisphere</t>
+          <t>a particular point or period in a process or development</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>level, phase, period</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>beginning, end, completion</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>South Africa is a country in Africa.</t>
+          <t>Jesus takes centre stage as Brazil win Copa America.</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>location</t>
         </is>
       </c>
     </row>
@@ -2851,52 +2838,352 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>দক্ষিণ</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>the direction or region to the right of east and to the left of west</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>southern, southward, southwards</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>north, northern, northward</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>South Africa and Pakistan battle for survival.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
           <t>proper noun</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>আফ্রিকা</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>a continent in the southern hemisphere</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>South Africa and Pakistan battle for survival.</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>battle</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>যুদ্ধ</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>a fight or struggle, especially a long and difficult one</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>fight, struggle, conflict</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>peace, harmony, tranquility</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>South Africa and Pakistan battle for survival.</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>survival</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>বেঁচে থাকা</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>the state of continuing to live or exist</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>existence, life, subsistence</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>death, extinction, annihilation</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>South Africa and Pakistan battle for survival.</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>পাকিস্তান</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>a country in South Asia</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Pakistan is playing in the tournament.</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>South Africa and Pakistan battle for survival.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>geography</t>
         </is>
       </c>
     </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>mighty</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>শক্তিশালী</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>very strong or powerful</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>strong, powerful, potent</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>weak, feeble, powerless</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>England is a mighty team in the tournament.</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>ইংল্যান্ড</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>a country in Northwest Europe</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>England is a mighty team in the tournament.</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J49"/>
+  <autoFilter ref="A4:J55"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -2915,19 +3202,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>DAILY STAR VOCABULARY ANALYSIS - BCS &amp; JOB EXAM FOCUS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>VOCABULARY BREAKDOWN BY LEVEL</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>VOCABULARY DISTRIBUTION BY NEWSPAPER SECTOR</t>
         </is>
@@ -2972,10 +3259,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0.6666666666666666</v>
+        <v>39</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="6">
@@ -2985,10 +3272,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.3111111111111111</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>0.2352941176470588</v>
       </c>
     </row>
     <row r="7">
@@ -2998,10 +3285,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0.02222222222222222</v>
+        <v>0</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3020,35 +3307,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>BANGLADESHI JOB EXAM PREPARATION GUIDELINES (BCS, BANK, NTRCA, PRIMARY)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>1. BCS Preliminary Strategy: Daily Star editorials contain high-frequency synonyms/antonyms asked directly in BCS Preliminary (20 Marks English). Focus on Advanced words.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>2. BCS Written Strategy: Words like 'Rupture', 'Reimagine', 'Transboundary', 'Exacerbate' enhance the standard of translation and passage writing in BCS Written.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>3. Bank Recruitment Exams: Bank exams heavily emphasize vocabulary in context, reading comprehension, and fill-in-the-blanks. Learn synonyms and precise nuances.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>4. Revision Technique: Practice making sentences using 5 new Daily Star vocabulary words daily to retain Bengali meaning and appropriate usage.</t>
         </is>
@@ -3082,403 +3369,403 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>DAILY STAR VOCABULARY PRACTICE SET (JOB EXAM MODEL TEST)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Test your vocabulary knowledge for upcoming BCS Preliminary, Combined Bank Officers, and Primary Teacher exams.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Q. No</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Question / Contextual Sentence</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Correct Answer &amp; Explanation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>What is a 'maiden' voyage?</t>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Which continent is home to the Sahara Desert?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A first trip by car</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A first trip by ship</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A first trip by plane</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A first trip by train</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>B — A 'maiden' voyage refers to the first trip or journey of a ship.</t>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>B — Africa is the continent where the Sahara Desert is located.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Which country is known for its Carnival celebrations?</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>What does 'amid' mean?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>surrounded by</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>located at</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>moving towards</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>C — Brazil is famous for its vibrant Carnival celebrations.</t>
+          <t>coming from</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>A — 'Amid' is a preposition that means being surrounded by something.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Which of the following is a term for the people of Afghanistan?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Africans</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Asians</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Afghans</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Europeans</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>C — Afghans refers to the people who are from Afghanistan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>What is the 'centre' of something?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>the edge</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>the corner</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>the middle</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>the top</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>C — The centre of something is the middle point of that thing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>What does 'boom' mean in the context of economy?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>a period of decline</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>a period of stagnation</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>a period of rapid growth</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>a period of stability</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>C — In the context of economy, 'boom' refers to a period of rapid growth or expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>What is the purpose of being at the 'top' of a competition?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>to lose</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>to draw</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>to win</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>to quit</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>C — The purpose of being at the top of a competition is to win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>What does 'top-heavy' mean?</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Having more weight at the bottom</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Having more weight at the top</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Having equal weight throughout</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Having no weight at all</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>B — 'Top-heavy' refers to something that has more weight or emphasis at the top.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>What is 'art'?</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>A type of science</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>A type of music</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>A type of creative expression</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>A type of sport</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>C — 'Art' refers to a wide range of creative expressions, including painting, sculpture, and music.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>What does it mean to 'win' something?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>To lose something</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>To gain something</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>To forget something</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>To give up something</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>B — To 'win' something means to gain or achieve it, often through competition or effort.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Which country is known for its love of tea and cricket?</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>America</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>C — England is famous for its love of tea and cricket.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>What does 'forgotten' mean?</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remembered clearly</t>
+          <t>having more weight at the bottom</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Not remembered at all</t>
+          <t>having more weight at the top</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Partially remembered</t>
+          <t>having equal weight throughout</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not important</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>B — 'Forgotten' means not remembered or no longer kept in mind.</t>
+          <t>having no weight</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>B — 'Top-heavy' means having more weight or emphasis at the top.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>What is a 'warm-up'?</t>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>What is 'murder'?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A cool-down exercise</t>
+          <t>the act of helping someone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A stretching exercise</t>
+          <t>the act of killing someone</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>An exercise to prepare for physical activity</t>
+          <t>the act of injuring someone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A type of sport</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>C — A 'warm-up' is an exercise or activity done to prepare the body for physical activity or sport.</t>
+          <t>the act of ignoring someone</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>B — Murder is the act of unlawfully killing another human being.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>What is a 'diary'?</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>What is 'Copa' likely to refer to in the context of sports?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A type of book for writing notes</t>
+          <t>a type of football stadium</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A type of book for writing stories</t>
+          <t>a type of football tournament</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A personal record of daily events and thoughts</t>
+          <t>a type of football player</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A type of calendar</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>C — A 'diary' is a personal record of daily events, thoughts, and feelings, often written in a book or digital format.</t>
+          <t>a type of football equipment</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>B — In the context of sports, 'Copa' likely refers to a type of football tournament, such as the Copa America.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Which of the following countries is often referred to as a 'melting pot' of cultures?</t>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>What is a 'stage' in the context of theater or performance?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>the audience</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>the actors</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>America</t>
+          <t>the area where the performance takes place</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>C — America is often referred to as a 'melting pot' of cultures due to its diverse population and history of immigration.</t>
+          <t>the script</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>C — In the context of theater or performance, the stage is the area where the performance takes place.</t>
         </is>
       </c>
     </row>

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, molestation, coercion</t>
+          <t>assault, molestation, abuse</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or focus</t>
+          <t>to change direction or course of action</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, change, adapt</t>
+          <t>shift, change, alter</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>energy</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -785,39 +785,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>a group of five</t>
+          <t>goods or products that are bought and sold</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>group, set</t>
+          <t>goods, merchandise</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>individual, alone</t>
+          <t>services, intangible</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The team scored two fifties in the match.</t>
+          <t>The price of commodities is fluctuating in the market.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -835,39 +835,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>a score of 50</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>goods, merchandise</t>
+          <t>fifty, fifty</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>services, intangibles</t>
+          <t>zero, negative</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The price of commodities has increased significantly.</t>
+          <t>The batsman scored a fifties in the match.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>guide</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -892,32 +892,32 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>কৌশল</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>a central point or location</t>
+          <t>to show someone the way</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>center, middle</t>
+          <t>lead, direct</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>mislead, confuse</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The stadium is located at the centre of the city.</t>
+          <t>The guide helped us navigate through the forest.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>travel</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>existence, life</t>
+          <t>center, middle</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>periphery, edge</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament is uncertain.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>boon</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>বর</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a benefit or advantage</t>
+          <t>a person or thing that is most important or prominent</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>advantage, benefit</t>
+          <t>star, main</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>disadvantage, loss</t>
+          <t>minor, secondary</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The new policy is a boon for the environment.</t>
+          <t>The centre of attention was the new product launch.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>people</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1035,34 +1035,34 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a group of five</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>group, set</t>
+          <t>fight, struggle</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>individual, alone</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team scored two fifties in the match.</t>
+          <t>The two teams are engaged in a battle for the championship.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1085,34 +1085,34 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>an exercise or activity to prepare for a competition</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>practice, rehearsal</t>
+          <t>existence, life</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>competition, game</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The team had a warm-up match before the tournament.</t>
+          <t>The team's survival in the tournament depends on their next game.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>a piece of advice or instruction</t>
+          <t>official accusations of wrongdoing</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>advice, guidance</t>
+          <t>accusations, allegations</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>mistake, error</t>
+          <t>innocence, exoneration</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The coach gave the team a lesson on teamwork.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1177,47 +1177,47 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
+          <t>framed</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>আকার দেওয়া</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>to put someone or something in a particular position</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>set, placed</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>removed, taken away</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>The picture was framed in a beautiful gold frame.</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
           <t>art</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>শিল্প</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>a skill or talent</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>skill, talent</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>mistake, error</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>The artist is known for her beautiful art.</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>culture</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the promotion of a product or service</t>
+          <t>the expression or application of human creative skill and imagination</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>marketing, promotion</t>
+          <t>craft, skill</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>sales, revenue</t>
+          <t>non-art, non-creative</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The company is investing in advertising to increase sales.</t>
+          <t>The museum features a collection of modern art.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -1292,27 +1292,27 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>the act of promoting or publicizing a product or service</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>promoting, publicizing</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>balanced, stable</t>
+          <t>hiding, concealing</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure is a major concern.</t>
+          <t>The company is investing heavily in advertising.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1342,37 +1342,187 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>গম্ভীর গর্জন</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>a central point or location</t>
+          <t>a sudden increase in something</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>center, middle</t>
+          <t>growth, expansion</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>decline, contraction</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The stadium is located at the centre of the city.</t>
+          <t>The economy is experiencing a boom in the tech sector.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>top-heavy</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>মাথাভারী</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>having too much weight or emphasis at the top</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>unbalanced, uneven</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>balanced, even</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>The company's top-heavy management structure is inefficient.</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>শিক্ষা</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>a piece of advice or a moral teaching</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>advice, teaching</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>ignorance, mistake</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>The coach taught the team a valuable lesson about teamwork.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>বাংলাদেশ</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>a country in South Asia</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>country, nation</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>city, state</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Bangladesh is a beautiful country with a rich culture.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>geography</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J19"/>
+  <autoFilter ref="A4:J22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1448,10 +1598,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.4</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -1461,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1474,10 +1624,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or course of action</t>
+          <t>to change direction or approach</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -785,39 +785,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>a score of 50</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>goods, merchandise</t>
+          <t>fifty, fifty</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>services, intangible</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities is fluctuating in the market.</t>
+          <t>The batsman scored a half-century in the match.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -835,39 +835,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>মূল্যবান পণ্য</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>a score of 50</t>
+          <t>goods or products that are bought and sold</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>fifty, fifty</t>
+          <t>goods, products</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>zero, negative</t>
+          <t>services</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The batsman scored a fifties in the match.</t>
+          <t>The price of commodities has increased significantly.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>guide</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -892,32 +892,32 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>কৌশল</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>to show someone the way</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>lead, direct</t>
+          <t>middle, center</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>mislead, confuse</t>
+          <t>periphery, edge</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The guide helped us navigate through the forest.</t>
+          <t>The city centre is bustling with activity.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>the middle or central part of something</t>
+          <t>a fight or struggle</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>center, middle</t>
+          <t>fight, struggle</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The city is located at the centre of the country.</t>
+          <t>The two teams are engaged in a fierce battle.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>war</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,39 +985,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a person or thing that is most important or prominent</t>
+          <t>the state of continuing to exist</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>star, main</t>
+          <t>existence, living</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>minor, secondary</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The centre of attention was the new product launch.</t>
+          <t>The team's survival in the tournament is uncertain.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>official accusations of wrongdoing</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>fight, struggle</t>
+          <t>accusations, allegations</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>peace, harmony</t>
+          <t>acquittal, exoneration</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The two teams are engaged in a battle for the championship.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1077,47 +1077,47 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>আকৃতি</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>to create or shape something</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>existence, life</t>
+          <t>created, shaped</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>destroyed, dismantled</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament depends on their next game.</t>
+          <t>The artist framed the painting in a beautiful frame.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>art</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1135,39 +1135,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>গম্ভীর গর্জন</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>official accusations of wrongdoing</t>
+          <t>a sudden increase in something</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>accusations, allegations</t>
+          <t>growth, expansion</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>innocence, exoneration</t>
+          <t>decline, contraction</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>The economy is experiencing a boom.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>advertisement</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>আকার দেওয়া</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>to put someone or something in a particular position</t>
+          <t>a public notice or announcement</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>set, placed</t>
+          <t>announcement, notice</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>removed, taken away</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The picture was framed in a beautiful gold frame.</t>
+          <t>The company placed an advertisement in the newspaper.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1235,9 +1235,9 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the expression or application of human creative skill and imagination</t>
+          <t>the expression or application of human creative skill</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>craft, skill</t>
+          <t>skill, craft</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>non-art, non-creative</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The museum features a collection of modern art.</t>
+          <t>The artist is a master of her art.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -1292,27 +1292,27 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>the act of promoting or publicizing a product or service</t>
+          <t>having too much at the top</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>promoting, publicizing</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>hiding, concealing</t>
+          <t>balanced, even</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The company is investing heavily in advertising.</t>
+          <t>The company's top-heavy structure is a problem.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>গম্ভীর গর্জন</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>a sudden increase in something</t>
+          <t>a piece of advice or guidance</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>growth, expansion</t>
+          <t>advice, guidance</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>decline, contraction</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The economy is experiencing a boom in the tech sector.</t>
+          <t>The teacher gave the student a valuable lesson.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>education</t>
         </is>
       </c>
     </row>
@@ -1377,47 +1377,47 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>win</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>পরিবারের জীবিকার্জক</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>to succeed or come out on top</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>succeed, triumph</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>balanced, even</t>
+          <t>lose, fail</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The company's top-heavy management structure is inefficient.</t>
+          <t>The team won the match.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1435,34 +1435,34 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>a piece of advice or a moral teaching</t>
+          <t>a preliminary exercise or activity</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>advice, teaching</t>
+          <t>exercise, activity</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>ignorance, mistake</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The coach taught the team a valuable lesson about teamwork.</t>
+          <t>The team had a warm-up session before the match.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1492,27 +1492,27 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>বাংলাদেশ</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>a country in South Asia</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>country, nation</t>
+          <t>middle, center</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>city, state</t>
+          <t>periphery, edge</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Bangladesh is a beautiful country with a rich culture.</t>
+          <t>The city centre is bustling with activity.</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1521,8 +1521,58 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>পর্যায়</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>a platform or area for performance</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>platform, area</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>The actor took the stage to perform.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>theatre</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J22"/>
+  <autoFilter ref="A4:J23"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1598,10 +1648,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.4210526315789473</v>
       </c>
     </row>
     <row r="6">
@@ -1614,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4736842105263158</v>
       </c>
     </row>
     <row r="7">
@@ -1624,10 +1674,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, permission</t>
+          <t>consent, agreement</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or approach</t>
+          <t>to change direction or focus</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>able to be replaced or restored</t>
+          <t>able to be restored or replenished naturally</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>a score of 50</t>
+          <t>the expression or application of human creative skill and imagination</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>fifty, fifty</t>
+          <t>craft, skill</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>science, technology</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The batsman scored a half-century in the match.</t>
+          <t>The art of painting is a popular hobby.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -842,32 +842,32 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>মূল্যবান পণ্য</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>having too much weight or emphasis at the top</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>goods, products</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>balanced, stable</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The price of commodities has increased significantly.</t>
+          <t>The company's top-heavy structure is making it difficult to manage.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -885,39 +885,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>মূল্যবান পণ্য</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>the middle or central part of something</t>
+          <t>goods or materials that can be bought and sold</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>middle, center</t>
+          <t>goods, merchandise</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>services, intangibles</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The city centre is bustling with activity.</t>
+          <t>The price of commodities is fluctuating in the market.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -927,47 +927,47 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>বেশি মূল্যবান</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>a fight or struggle</t>
+          <t>more expensive or valuable</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>fight, struggle</t>
+          <t>costlier, pricier</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>peace, harmony</t>
+          <t>cheaper, less valuable</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The two teams are engaged in a fierce battle.</t>
+          <t>The new smartphone is dearer than the old one.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>war</t>
+          <t>finance</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,39 +985,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>পঞ্চাশের দশক</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>the state of continuing to exist</t>
+          <t>the decade from 1950 to 1959</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>existence, living</t>
+          <t>fifties, fifty</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>sixties, sixty</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament is uncertain.</t>
+          <t>The fifties were a time of great social change.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>official accusations of wrongdoing</t>
+          <t>a preliminary exercise or activity to prepare for a main event</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>accusations, allegations</t>
+          <t>preliminary, preparatory</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>acquittal, exoneration</t>
+          <t>main, final</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>The team had a warm-up session before the match.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1077,47 +1077,47 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>আকৃতি</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>to create or shape something</t>
+          <t>a central or middle point</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>created, shaped</t>
+          <t>center, middle</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>destroyed, dismantled</t>
+          <t>edge, periphery</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The artist framed the painting in a beautiful frame.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>গম্ভীর গর্জন</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>a sudden increase in something</t>
+          <t>a platform or area for performing or presenting</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>growth, expansion</t>
+          <t>platform, arena</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>decline, contraction</t>
+          <t>background, setting</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The economy is experiencing a boom.</t>
+          <t>The actor took the stage to deliver his speech.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>theater</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>advertisement</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1185,39 +1185,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a public notice or announcement</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>announcement, notice</t>
+          <t>fight, struggle</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The company placed an advertisement in the newspaper.</t>
+          <t>The two teams are battling for the championship.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1235,39 +1235,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the expression or application of human creative skill</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>skill, craft</t>
+          <t>existence, life</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The artist is a master of her art.</t>
+          <t>The team is fighting for survival in the league.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>having too much at the top</t>
+          <t>official accusations or complaints made against someone</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>accusations, complaints</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>balanced, even</t>
+          <t>acquittals, pardons</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure is a problem.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1327,47 +1327,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>আকৃতি দেওয়া</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>a piece of advice or guidance</t>
+          <t>to be officially accused or charged with a crime</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>advice, guidance</t>
+          <t>charged, accused</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>acquitted, pardoned</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The teacher gave the student a valuable lesson.</t>
+          <t>The suspect was framed for the crime.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1392,32 +1392,32 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>পরিবারের জীবিকার্জক</t>
+          <t>নাম</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>to succeed or come out on top</t>
+          <t>a word or phrase used to identify someone or something</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>succeed, triumph</t>
+          <t>label, title</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>lose, fail</t>
+          <t>secret, anonymous</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The team won the match.</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>communication</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>mention</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>উল্লেখ করা</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>a preliminary exercise or activity</t>
+          <t>to refer to or speak about someone or something</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>exercise, activity</t>
+          <t>refer, speak</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ignore, neglect</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The team had a warm-up session before the match.</t>
+          <t>Please mention my name in the report.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>communication</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1492,87 +1492,37 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>নতুন</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>the middle or central part of something</t>
+          <t>recently created or discovered</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>middle, center</t>
+          <t>recent, modern</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>old, outdated</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>The city centre is bustling with activity.</t>
+          <t>The new smartphone is very popular.</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>stage</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>পর্যায়</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>a platform or area for performance</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>platform, area</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>The actor took the stage to perform.</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>theatre</t>
+          <t>general</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J23"/>
+  <autoFilter ref="A4:J22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1648,10 +1598,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -1661,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="7">
@@ -1674,10 +1624,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -657,17 +657,17 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, agreement</t>
+          <t>consent, permission, agreement</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating the rape case.</t>
+          <t>The police are investigating a rape case.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>crime</t>
+          <t>Crime</t>
         </is>
       </c>
     </row>
@@ -697,17 +697,17 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or focus</t>
+          <t>to change direction or course of action</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, change, alter</t>
+          <t>shift, turn, change</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>remain, stay</t>
+          <t>remain, stay, continue</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly</t>
+          <t>sustainable, eco-friendly, green</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, finite</t>
+          <t>non-renewable, finite, limited</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -802,22 +802,22 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>craft, skill</t>
+          <t>craft, skill, technique</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>science, technology</t>
+          <t>science, technology, engineering</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The art of painting is a popular hobby.</t>
+          <t>The artist's latest sculpture is a masterpiece of modern art.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>Culture</t>
         </is>
       </c>
     </row>
@@ -835,9 +835,9 @@
           <t>adjective</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -852,22 +852,22 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>unbalanced, uneven, disproportionate</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>balanced, stable</t>
+          <t>balanced, even, proportional</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure is making it difficult to manage.</t>
+          <t>The company's top-heavy management structure needs to be reformed.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -897,27 +897,27 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>goods or materials that can be bought and sold</t>
+          <t>goods or products that are bought and sold in large quantities</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>goods, merchandise</t>
+          <t>goods, products, merchandise</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles</t>
+          <t>services, intangibles, non-material</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities is fluctuating in the market.</t>
+          <t>The price of commodities has been fluctuating wildly in recent months.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>বেশি মূল্যবান</t>
+          <t>পঞ্চাশের দশক</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>more expensive or valuable</t>
+          <t>the numbers 50 to 59</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>costlier, pricier</t>
+          <t>fifty, fifty-something, middle-aged</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>cheaper, less valuable</t>
+          <t>young, old, elderly</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The new smartphone is dearer than the old one.</t>
+          <t>The fifties are a challenging time for many people.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>Demographics</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশের দশক</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>the decade from 1950 to 1959</t>
+          <t>a middle point or location</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>fifties, fifty</t>
+          <t>middle, center, midpoint</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>sixties, sixty</t>
+          <t>edge, periphery, extremity</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The fifties were a time of great social change.</t>
+          <t>The city's centre is a bustling hub of activity.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a preliminary exercise or activity to prepare for a main event</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>preliminary, preparatory</t>
+          <t>existence, life, livelihood</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>main, final</t>
+          <t>death, extinction, demise</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team had a warm-up session before the match.</t>
+          <t>The team's survival in the tournament depends on their next match.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Life</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>boon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1085,39 +1085,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>বর</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>a central or middle point</t>
+          <t>a benefit or advantage</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>center, middle</t>
+          <t>advantage, benefit, gain</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>edge, periphery</t>
+          <t>disadvantage, loss, setback</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The city is located at the centre of the country.</t>
+          <t>The new policy is a boon for the environment.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>Society</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>পঞ্চাশের দশক</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>a platform or area for performing or presenting</t>
+          <t>the numbers 50 to 59</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>platform, arena</t>
+          <t>fifty, fifty-something, middle-aged</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>background, setting</t>
+          <t>young, old, elderly</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The actor took the stage to deliver his speech.</t>
+          <t>The fifties are a challenging time for many people.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>theater</t>
+          <t>Demographics</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1185,39 +1185,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>an activity or exercise to prepare for a main event</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle</t>
+          <t>preparation, rehearsal, practice</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony</t>
+          <t>cool-down, relaxation, leisure</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The two teams are battling for the championship.</t>
+          <t>The team had a warm-up session before the game.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1235,39 +1235,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>a middle point or location</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>existence, life</t>
+          <t>middle, center, midpoint</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>edge, periphery, extremity</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The team is fighting for survival in the league.</t>
+          <t>The city's centre is a bustling hub of activity.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1292,32 +1292,32 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>official accusations or complaints made against someone</t>
+          <t>a place or situation where something happens or is presented</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>accusations, complaints</t>
+          <t>platform, arena, setting</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>acquittals, pardons</t>
+          <t>background, context, environment</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>The play is being performed on stage tonight.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>আকৃতি দেওয়া</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>to be officially accused or charged with a crime</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>charged, accused</t>
+          <t>fight, struggle, conflict</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>acquitted, pardoned</t>
+          <t>peace, harmony, agreement</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The suspect was framed for the crime.</t>
+          <t>The two teams are engaged in a fierce battle for the championship.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>Conflict</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1385,39 +1385,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>নাম</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>a word or phrase used to identify someone or something</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>label, title</t>
+          <t>existence, life, livelihood</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>secret, anonymous</t>
+          <t>death, extinction, demise</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>What is your name?</t>
+          <t>The team's survival in the tournament depends on their next match.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Life</t>
         </is>
       </c>
     </row>
@@ -1427,102 +1427,52 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>mention</t>
+          <t>boon</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>উল্লেখ করা</t>
+          <t>বর</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>to refer to or speak about someone or something</t>
+          <t>a benefit or advantage</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>refer, speak</t>
+          <t>advantage, benefit, gain</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>ignore, neglect</t>
+          <t>disadvantage, loss, setback</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Please mention my name in the report.</t>
+          <t>The new policy is a boon for the environment.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>নতুন</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>recently created or discovered</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>recent, modern</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>old, outdated</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>The new smartphone is very popular.</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>general</t>
+          <t>Society</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J22"/>
+  <autoFilter ref="A4:J21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1598,10 +1548,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.5</v>
+        <v>0.3529411764705883</v>
       </c>
     </row>
     <row r="6">
@@ -1611,10 +1561,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="7">
@@ -1624,10 +1574,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2352941176470588</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, molestation, abuse</t>
+          <t>assault, molestation, molestation</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, permission, agreement</t>
+          <t>consent, permission</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Crime</t>
+          <t>crime</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, turn, change</t>
+          <t>shift, change, alter</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>able to be restored or replenished naturally</t>
+          <t>able to be replaced or restored</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>energy</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The artist's latest sculpture is a masterpiece of modern art.</t>
+          <t>The art of painting is a beautiful form of self-expression.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The company's top-heavy management structure needs to be reformed.</t>
+          <t>The company's top-heavy management structure is a major issue.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>মূল্যবান পণ্য</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold in large quantities</t>
+          <t>goods or products that are bought and sold on a market</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles, non-material</t>
+          <t>services, intangibles, non-tangibles</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities has been fluctuating wildly in recent months.</t>
+          <t>The price of commodities has been rising in recent months.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>পঞ্চাশের দশক</t>
+          <t>বেশি ব্যয়বহুল</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>the numbers 50 to 59</t>
+          <t>more expensive</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>fifty, fifty-something, middle-aged</t>
+          <t>costlier, pricier, more expensive</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>young, old, elderly</t>
+          <t>cheaper, less expensive, less costly</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The fifties are a challenging time for many people.</t>
+          <t>The new smartphone is dearer than the old one.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Demographics</t>
+          <t>finance</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a middle point or location</t>
+          <t>a decade of the 20th century</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>middle, center, midpoint</t>
+          <t>fifty, fifty, half-century</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>edge, periphery, extremity</t>
+          <t>sixties, seventies, eighties</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The city's centre is a bustling hub of activity.</t>
+          <t>The fifties were a great time for music and fashion.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>a preliminary exercise or activity to prepare for a main event</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>existence, life, livelihood</t>
+          <t>preliminary, preparatory, introductory</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>death, extinction, demise</t>
+          <t>main, final, conclusive</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament depends on their next match.</t>
+          <t>The team had a warm-up match before the tournament.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>boon</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1085,39 +1085,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>বর</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>a benefit or advantage</t>
+          <t>a central or middle point</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>advantage, benefit, gain</t>
+          <t>center, middle, midpoint</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>disadvantage, loss, setback</t>
+          <t>periphery, edge, boundary</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The new policy is a boon for the environment.</t>
+          <t>The city's centre is a bustling area with shops and restaurants.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Society</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>পঞ্চাশের দশক</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>the numbers 50 to 59</t>
+          <t>a particular point in a process or situation</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>fifty, fifty-something, middle-aged</t>
+          <t>step, phase, phase</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>young, old, elderly</t>
+          <t>end, conclusion, finish</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The fifties are a challenging time for many people.</t>
+          <t>The play is on stage now.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Demographics</t>
+          <t>theater</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1185,39 +1185,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>an activity or exercise to prepare for a main event</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>preparation, rehearsal, practice</t>
+          <t>fight, struggle, conflict</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>cool-down, relaxation, leisure</t>
+          <t>peace, harmony, cooperation</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The team had a warm-up session before the game.</t>
+          <t>The two teams are battling for the championship.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1235,39 +1235,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>a middle point or location</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>middle, center, midpoint</t>
+          <t>existence, life, living</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>edge, periphery, extremity</t>
+          <t>death, demise, extinction</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The city's centre is a bustling hub of activity.</t>
+          <t>The team's survival in the tournament is uncertain.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1292,32 +1292,32 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>a place or situation where something happens or is presented</t>
+          <t>a formal accusation of a crime or wrongdoing</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>platform, arena, setting</t>
+          <t>accusation, indictment, allegation</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>background, context, environment</t>
+          <t>acquittal, exoneration, clearance</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The play is being performed on stage tonight.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>আবিষ্কৃত</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>to be formally accused or charged with a crime</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>fight, struggle, conflict</t>
+          <t>accused, indicted, charged</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>peace, harmony, agreement</t>
+          <t>exonerated, cleared, acquitted</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The two teams are engaged in a fierce battle for the championship.</t>
+          <t>The suspect has been framed for the crime.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1385,39 +1385,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>নাম</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>a word or phrase used to identify someone or something</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>existence, life, livelihood</t>
+          <t>title, label, designation</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>death, extinction, demise</t>
+          <t>anonymity, pseudonym, alias</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament depends on their next match.</t>
+          <t>What's your name?</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>identity</t>
         </is>
       </c>
     </row>
@@ -1427,47 +1427,47 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>boon</t>
+          <t>must</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>বর</t>
+          <t>অবশ্যই</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>a benefit or advantage</t>
+          <t>to be necessary or obligatory</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>advantage, benefit, gain</t>
+          <t>need, require, necessitate</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>disadvantage, loss, setback</t>
+          <t>optional, voluntary, discretionary</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The new policy is a boon for the environment.</t>
+          <t>You must wear a helmet when riding a bike.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Society</t>
+          <t>obligation</t>
         </is>
       </c>
     </row>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.5294117647058824</v>
       </c>
     </row>
     <row r="6">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3529411764705883</v>
       </c>
     </row>
     <row r="7">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, molestation, molestation</t>
+          <t>assault, molestation, molester</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, permission</t>
+          <t>consent, agreement</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating a rape case.</t>
+          <t>The police are investigating the rape case.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>crime</t>
+          <t>Crime</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>remain, stay, continue</t>
+          <t>remain, stay</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>The company needs to pivot its strategy to stay competitive.</t>
+          <t>The company will pivot its strategy to focus on renewable energy.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>adj</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly, green</t>
+          <t>sustainable, eco-friendly</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, finite, limited</t>
+          <t>non-renewable, unsustainable</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>the expression or application of human creative skill and imagination</t>
+          <t>a decade of years, specifically 50-59</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>craft, skill, technique</t>
+          <t>fifty, fifty years old</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>science, technology, engineering</t>
+          <t>thirties, twenties</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The art of painting is a beautiful form of self-expression.</t>
+          <t>Mushfiqur played a great innings in his fifties.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>Age</t>
         </is>
       </c>
     </row>
@@ -827,47 +827,47 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>মূল্যবান পণ্য</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>goods or products that can be bought and sold</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, uneven, disproportionate</t>
+          <t>goods, products, merchandise</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>balanced, even, proportional</t>
+          <t>services, intangibles</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The company's top-heavy management structure is a major issue.</t>
+          <t>The price of commodities is increasing rapidly.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -877,47 +877,47 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>বেশি মূল্যবান</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold on a market</t>
+          <t>more expensive or valuable</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>goods, products, merchandise</t>
+          <t>costlier, pricier</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles, non-tangibles</t>
+          <t>cheaper, less expensive</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities has been rising in recent months.</t>
+          <t>The new smartphone is dearer than the old one.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>tigers</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>বেশি ব্যয়বহুল</t>
+          <t>বাঘ</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>more expensive</t>
+          <t>large carnivorous mammals</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>costlier, pricier, more expensive</t>
+          <t>lions, leopards, cheetahs</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>cheaper, less expensive, less costly</t>
+          <t>herbivores, omnivores</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The new smartphone is dearer than the old one.</t>
+          <t>The Bangladesh cricket team is called the Tigers.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>Animals</t>
         </is>
       </c>
     </row>
@@ -977,47 +977,47 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a decade of the 20th century</t>
+          <t>a central or middle point</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>fifty, fifty, half-century</t>
+          <t>middle, center, midpoint</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>sixties, seventies, eighties</t>
+          <t>periphery, edge</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The fifties were a great time for music and fashion.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
@@ -1027,47 +1027,47 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a preliminary exercise or activity to prepare for a main event</t>
+          <t>a platform or area for performance or display</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>preliminary, preparatory, introductory</t>
+          <t>platform, platform, stage, arena</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>main, final, conclusive</t>
+          <t>background, setting</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team had a warm-up match before the tournament.</t>
+          <t>The actor took the stage to perform the play.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
@@ -1077,47 +1077,47 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>a central or middle point</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>center, middle, midpoint</t>
+          <t>fight, struggle, conflict</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>periphery, edge, boundary</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The city's centre is a bustling area with shops and restaurants.</t>
+          <t>The two teams are engaged in a fierce battle for the championship.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>Conflict</t>
         </is>
       </c>
     </row>
@@ -1127,47 +1127,47 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>a particular point in a process or situation</t>
+          <t>the state of continuing to live or exist</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>step, phase, phase</t>
+          <t>existence, life, livelihood</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>end, conclusion, finish</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The play is on stage now.</t>
+          <t>The team is fighting for survival in the league.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>theater</t>
+          <t>Life</t>
         </is>
       </c>
     </row>
@@ -1177,47 +1177,47 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>the expression or application of human creative skill and imagination</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle, conflict</t>
+          <t>craft, skill, technique</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony, cooperation</t>
+          <t>science, technology</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The two teams are battling for the championship.</t>
+          <t>The artist is known for her beautiful paintings.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Creativity</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>the promotion of a product or service through various media</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>existence, life, living</t>
+          <t>marketing, promotion, publicity</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>death, demise, extinction</t>
+          <t>hiding, concealment</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament is uncertain.</t>
+          <t>The company is investing heavily in advertising.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>boast</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>অহংকার করা</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>a formal accusation of a crime or wrongdoing</t>
+          <t>to talk proudly about one's achievements or possessions</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>accusation, indictment, allegation</t>
+          <t>brag, boast, vaunt</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>acquittal, exoneration, clearance</t>
+          <t>hide, conceal</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>He likes to boast about his wealth.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>Pride</t>
         </is>
       </c>
     </row>
@@ -1327,47 +1327,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>আবিষ্কৃত</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>to be formally accused or charged with a crime</t>
+          <t>a piece of advice or a moral teaching</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>accused, indicted, charged</t>
+          <t>advice, guidance, counsel</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>exonerated, cleared, acquitted</t>
+          <t>ignorance, foolishness</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The suspect has been framed for the crime.</t>
+          <t>The teacher gave the students a valuable lesson.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -1377,47 +1377,47 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>নাম</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>a word or phrase used to identify someone or something</t>
+          <t>having too much weight or emphasis at the top</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>title, label, designation</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>anonymity, pseudonym, alias</t>
+          <t>balanced, even</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>What's your name?</t>
+          <t>The company's top-heavy structure is causing problems.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>must</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1442,37 +1442,87 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>অবশ্যই</t>
+          <t>গম্ভীর গর্জন</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>to be necessary or obligatory</t>
+          <t>a sudden and rapid increase in something</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>need, require, necessitate</t>
+          <t>growth, expansion, surge</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>optional, voluntary, discretionary</t>
+          <t>decline, contraction</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>You must wear a helmet when riding a bike.</t>
+          <t>The economy is experiencing a boom.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>obligation</t>
+          <t>Economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>charges</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>অভিযোগ</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>a formal accusation of a crime or wrongdoing</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>accusation, indictment, complaint</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>acquittal, exoneration</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>The police have filed charges against the suspect.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Law</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J21"/>
+  <autoFilter ref="A4:J22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1548,10 +1598,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="6">
@@ -1561,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="7">
@@ -1574,10 +1624,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, molestation, molester</t>
+          <t>assault, molestation, abuse</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, agreement</t>
+          <t>consent, permission</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating the rape case.</t>
+          <t>The police are investigating a rape case.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or course of action</t>
+          <t>to change direction or approach</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, change, alter</t>
+          <t>shift, turn, alter</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>The company will pivot its strategy to focus on renewable energy.</t>
+          <t>The company needs to pivot its strategy to stay competitive.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>adj</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, unsustainable</t>
+          <t>non-renewable, finite</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>পঞ্চাশের</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>a decade of years, specifically 50-59</t>
+          <t>a score of 50</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>fifty, fifty years old</t>
+          <t>fifty, fifty</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>thirties, twenties</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Mushfiqur played a great innings in his fifties.</t>
+          <t>The batsman scored a fifties in the match.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -842,32 +842,32 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>মূল্যবান পণ্য</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>goods or products that can be bought and sold</t>
+          <t>a central part or position</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>goods, products, merchandise</t>
+          <t>center, middle</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>services, intangibles</t>
+          <t>periphery, edge</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The price of commodities is increasing rapidly.</t>
+          <t>The stadium has a large centre with a seating capacity of 50,000.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -877,47 +877,47 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>adj</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>বেশি মূল্যবান</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>more expensive or valuable</t>
+          <t>goods or products that are bought and sold</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>costlier, pricier</t>
+          <t>goods, merchandise</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>cheaper, less expensive</t>
+          <t>services, intangibles</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The new smartphone is dearer than the old one.</t>
+          <t>The prices of commodities have increased due to inflation.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>tigers</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>বাঘ</t>
+          <t>বেশি দামী</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>large carnivorous mammals</t>
+          <t>more expensive</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>lions, leopards, cheetahs</t>
+          <t>costlier, pricier</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>herbivores, omnivores</t>
+          <t>cheaper, less expensive</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The Bangladesh cricket team is called the Tigers.</t>
+          <t>The new smartphone is dearer than the previous model.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a central or middle point</t>
+          <t>a practice session or exercise to prepare for a competition</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>middle, center, midpoint</t>
+          <t>practice, rehearsal</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>competition, game</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The city is located at the centre of the country.</t>
+          <t>The team had a warm-up session before the match.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1027,47 +1027,47 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>Copa</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>বিশপ-সংক্রান্ত</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a platform or area for performance or display</t>
+          <t>a South American football tournament</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>platform, platform, stage, arena</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>background, setting</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The actor took the stage to perform the play.</t>
+          <t>Brazil won the Copa America title.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1092,32 +1092,32 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle, conflict</t>
+          <t>existence, living</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The two teams are engaged in a fierce battle for the championship.</t>
+          <t>The team's survival in the tournament depends on their next match.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>forgotten</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>বিস্মৃত</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to live or exist</t>
+          <t>not remembered or considered</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>existence, life, livelihood</t>
+          <t>overlooked, neglected</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>remembered, considered</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The team is fighting for survival in the league.</t>
+          <t>The art of Bengali advertising has been forgotten over time.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1197,27 +1197,27 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>the expression or application of human creative skill and imagination</t>
+          <t>a skill or talent used to create something</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>craft, skill, technique</t>
+          <t>craft, skill</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>science, technology</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The artist is known for her beautiful paintings.</t>
+          <t>The artist's latest painting is a masterpiece of art.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Creativity</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the promotion of a product or service through various media</t>
+          <t>the act of promoting a product or service</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>marketing, promotion, publicity</t>
+          <t>marketing, promotion</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>hiding, concealment</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>boast</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>v</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>অহংকার করা</t>
+          <t>গম্ভীর গর্জন</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>to talk proudly about one's achievements or possessions</t>
+          <t>a sudden increase in something</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>brag, boast, vaunt</t>
+          <t>growth, expansion</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>hide, conceal</t>
+          <t>decline, contraction</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>He likes to boast about his wealth.</t>
+          <t>The economy is experiencing a boom due to the new policies.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Pride</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -1327,47 +1327,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>a piece of advice or a moral teaching</t>
+          <t>having too much weight or emphasis at the top</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>advice, guidance, counsel</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>ignorance, foolishness</t>
+          <t>balanced, even</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The teacher gave the students a valuable lesson.</t>
+          <t>The team's top-heavy lineup made them vulnerable to counter-attacks.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1377,47 +1377,47 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>adj</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>a piece of advice or a moral</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>advice, guidance</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>balanced, even</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure is causing problems.</t>
+          <t>The coach gave the team a lesson on teamwork.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1427,47 +1427,47 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>Mithun</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>গম্ভীর গর্জন</t>
+          <t>মিথুন</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>a sudden and rapid increase in something</t>
+          <t>a Bangladeshi cricketer</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>growth, expansion, surge</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>decline, contraction</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The economy is experiencing a boom.</t>
+          <t>Mithun scored a fifties in the match.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1477,47 +1477,47 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>Mushfiqur</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>proper noun</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>মুশফিকুর</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>a formal accusation of a crime or wrongdoing</t>
+          <t>a Bangladeshi cricketer</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>accusation, indictment, complaint</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>acquittal, exoneration</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>Mushfiqur scored a fifties in the match.</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating a rape case.</t>
+          <t>The police are investigating the rape case.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or approach</t>
+          <t>to change direction or course of action</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, turn, alter</t>
+          <t>shift, change, alter</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>remain, stay</t>
+          <t>remain, stay, continue</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>able to be replaced or restored</t>
+          <t>able to be restored or replenished naturally</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly</t>
+          <t>sustainable, eco-friendly, green</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, finite</t>
+          <t>non-renewable, finite, exhaustible</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশের</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>a score of 50</t>
+          <t>a skill or talent that is developed through practice and study</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>fifty, fifty</t>
+          <t>craft, skill, technique</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>science, technology, engineering</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The batsman scored a fifties in the match.</t>
+          <t>She is a skilled artist.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Culture</t>
         </is>
       </c>
     </row>
@@ -827,47 +827,47 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>a central part or position</t>
+          <t>having too much weight or emphasis at the top</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>center, middle</t>
+          <t>unbalanced, uneven, disproportionate</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>periphery, edge</t>
+          <t>balanced, even, proportional</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The stadium has a large centre with a seating capacity of 50,000.</t>
+          <t>The company's top-heavy structure is a major concern.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -892,27 +892,27 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>মূল্যবান পণ্য</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>goods or products that are bought and sold in large quantities</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>goods, merchandise</t>
+          <t>goods, products, merchandise</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles</t>
+          <t>services, intangibles, abstracts</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The prices of commodities have increased due to inflation.</t>
+          <t>The price of commodities has been fluctuating recently.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>বেশি দামী</t>
+          <t>বেশি মূল্যবান</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>more expensive</t>
+          <t>more expensive or valuable</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>costlier, pricier</t>
+          <t>costlier, pricier, more valuable</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>cheaper, less expensive</t>
+          <t>cheaper, less valuable, worthless</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The new smartphone is dearer than the previous model.</t>
+          <t>The new smartphone is dearer than the old one.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,39 +985,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>পঞ্চাশের দশক</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a practice session or exercise to prepare for a competition</t>
+          <t>a decade of the 20th century</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>practice, rehearsal</t>
+          <t>fifties, fifty, fifty-year-olds</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>competition, game</t>
+          <t>sixties, sixty, sixty-year-olds</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The team had a warm-up session before the match.</t>
+          <t>The fifties were a time of great change.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -1027,42 +1027,42 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Copa</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>বিশপ-সংক্রান্ত</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>a South American football tournament</t>
+          <t>an exercise or activity to prepare for a competition or event</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>practice, rehearsal, preparation</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>competition, event, performance</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Brazil won the Copa America title.</t>
+          <t>The team had a warm-up match before the tournament.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1085,39 +1085,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>a central or middle point</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>existence, living</t>
+          <t>center, middle, core</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>edge, periphery, outer</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament depends on their next match.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -1127,42 +1127,42 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>forgotten</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>বিস্মৃত</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>not remembered or considered</t>
+          <t>a platform or area for performing or presenting</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>overlooked, neglected</t>
+          <t>platform, stage, platform</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>remembered, considered</t>
+          <t>backstage, offstage, behind</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The art of Bengali advertising has been forgotten over time.</t>
+          <t>The actor took the stage for the performance.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1185,39 +1185,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a skill or talent used to create something</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>craft, skill</t>
+          <t>fight, struggle, conflict</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>peace, harmony, agreement</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The artist's latest painting is a masterpiece of art.</t>
+          <t>The two teams are battling for the championship.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the act of promoting a product or service</t>
+          <t>the state of continuing to live or exist</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>marketing, promotion</t>
+          <t>existence, life, livelihood</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>death, extinction, demise</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The company is investing heavily in advertising.</t>
+          <t>The team's survival in the tournament depends on their next match.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1292,32 +1292,32 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>গম্ভীর গর্জন</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>a sudden increase in something</t>
+          <t>a formal accusation or complaint</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>growth, expansion</t>
+          <t>accusation, complaint, indictment</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>decline, contraction</t>
+          <t>acquittal, exoneration, pardon</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The economy is experiencing a boom due to the new policies.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Law</t>
         </is>
       </c>
     </row>
@@ -1327,47 +1327,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>আকৃতি</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>to create a picture or image in a frame</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>created, made, constructed</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>balanced, even</t>
+          <t>destroyed, ruined, damaged</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The team's top-heavy lineup made them vulnerable to counter-attacks.</t>
+          <t>The artist framed the painting in a beautiful frame.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1392,32 +1392,32 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>নাম</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>a piece of advice or a moral</t>
+          <t>a word or phrase used to identify someone or something</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>advice, guidance</t>
+          <t>title, label, designation</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unknown, anonymous, unnamed</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The coach gave the team a lesson on teamwork.</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
@@ -1427,102 +1427,52 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Mithun</t>
+          <t>must</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>proper noun</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>মিথুন</t>
+          <t>অবশ্যই</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>a Bangladeshi cricketer</t>
+          <t>to be necessary or required</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>need, require, demand</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>don't need, don't require, don't demand</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Mithun scored a fifties in the match.</t>
+          <t>You must wear a seatbelt while driving.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mushfiqur</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>proper noun</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>মুশফিকুর</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>a Bangladeshi cricketer</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Mushfiqur scored a fifties in the match.</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Sports</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J22"/>
+  <autoFilter ref="A4:J21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1598,10 +1548,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="6">
@@ -1611,10 +1561,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.5</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="7">
@@ -1624,10 +1574,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating the rape case.</t>
+          <t>The police are investigating a rape case.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Crime</t>
+          <t>crime</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or course of action</t>
+          <t>to change direction or approach</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>remain, stay, continue</t>
+          <t>remain, stay</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -747,17 +747,17 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>able to be restored or replenished naturally</t>
+          <t>able to be replaced or restored</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly, green</t>
+          <t>sustainable, eco-friendly</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, finite, exhaustible</t>
+          <t>non-renewable, finite</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>energy</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>a skill or talent that is developed through practice and study</t>
+          <t>a score of 50 in a game or sport</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>craft, skill, technique</t>
+          <t>score, points</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>science, technology, engineering</t>
+          <t>zero, loss</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>She is a skilled artist.</t>
+          <t>The team scored 50 runs in the fifties.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -827,47 +827,47 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>goods or products that are bought and sold</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, uneven, disproportionate</t>
+          <t>goods, merchandise</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>balanced, even, proportional</t>
+          <t>services, intangible</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure is a major concern.</t>
+          <t>The price of commodities has increased significantly.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>economics</t>
         </is>
       </c>
     </row>
@@ -877,47 +877,47 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>মূল্যবান পণ্য</t>
+          <t>বেশি ব্যয়বহুল</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold in large quantities</t>
+          <t>more expensive</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>goods, products, merchandise</t>
+          <t>costly, pricey</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles, abstracts</t>
+          <t>cheaper, affordable</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities has been fluctuating recently.</t>
+          <t>The new phone is dearer than the old one.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>finance</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>বেশি মূল্যবান</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>more expensive or valuable</t>
+          <t>the middle or most important part of something</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>costlier, pricier, more valuable</t>
+          <t>middle, center</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>cheaper, less valuable, worthless</t>
+          <t>edge, periphery</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The new smartphone is dearer than the old one.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,39 +985,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশের দশক</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a decade of the 20th century</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>fifties, fifty, fifty-year-olds</t>
+          <t>fight, struggle, conflict</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>sixties, sixty, sixty-year-olds</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The fifties were a time of great change.</t>
+          <t>The two teams are engaged in a fierce battle.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>an exercise or activity to prepare for a competition or event</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>practice, rehearsal, preparation</t>
+          <t>existence, life</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>competition, event, performance</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team had a warm-up match before the tournament.</t>
+          <t>The team's survival in the tournament is uncertain.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1092,32 +1092,32 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>a central or middle point</t>
+          <t>the expression or application of human creative skill and imagination</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>center, middle, core</t>
+          <t>craft, skill</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>edge, periphery, outer</t>
+          <t>science, technology</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The city is located at the centre of the country.</t>
+          <t>The artist is known for her beautiful paintings.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>শিক্ষা</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>a platform or area for performing or presenting</t>
+          <t>something that is learned or taught</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>platform, stage, platform</t>
+          <t>knowledge, wisdom</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>backstage, offstage, behind</t>
+          <t>ignorance, foolishness</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The actor took the stage for the performance.</t>
+          <t>The teacher gave a lesson on history.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>education</t>
         </is>
       </c>
     </row>
@@ -1177,47 +1177,47 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>having too much at the top and not enough at the bottom</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle, conflict</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony, agreement</t>
+          <t>balanced, stable</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The two teams are battling for the championship.</t>
+          <t>The company's top-heavy structure is a major concern.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>boon</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1235,39 +1235,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>বর</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to live or exist</t>
+          <t>a benefit or advantage</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>existence, life, livelihood</t>
+          <t>advantage, benefit</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>death, extinction, demise</t>
+          <t>disadvantage, loss</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament depends on their next match.</t>
+          <t>The new policy is a boon for the environment.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>society</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>win</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1292,32 +1292,32 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>পরিবারের জীবিকার্জক</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>a formal accusation or complaint</t>
+          <t>to succeed or achieve something</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>accusation, complaint, indictment</t>
+          <t>succeed, achieve</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>acquittal, exoneration, pardon</t>
+          <t>lose, fail</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>The team won the match.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1327,47 +1327,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>আকৃতি</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>to create a picture or image in a frame</t>
+          <t>an activity or exercise done to prepare for something</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>created, made, constructed</t>
+          <t>exercise, preparation</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>destroyed, ruined, damaged</t>
+          <t>relaxation, leisure</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The artist framed the painting in a beautiful frame.</t>
+          <t>The team did a warm-up before the game.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1392,32 +1392,32 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>নাম</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>a word or phrase used to identify someone or something</t>
+          <t>the middle or most important part of something</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>title, label, designation</t>
+          <t>middle, center</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>unknown, anonymous, unnamed</t>
+          <t>edge, periphery</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>What is your name?</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>geography</t>
         </is>
       </c>
     </row>
@@ -1427,52 +1427,152 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>must</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>পর্যায়</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>a place or situation where something happens or is performed</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>place, location</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>absence, void</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>The play is being performed on stage.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>takes</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
           <t>verb</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>অবশ্যই</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>to be necessary or required</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>need, require, demand</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>don't need, don't require, don't demand</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>You must wear a seatbelt while driving.</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Language</t>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>গ্রহণ করা</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>to accept or receive something</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>accept, receive</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>reject, refuse</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>The team takes the lead in the tournament.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Copa</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>বিশপ-সংক্রান্ত</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>a trophy or championship in football</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>trophy, championship</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>defeat, loss</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>The team won the Copa America.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>sports</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J21"/>
+  <autoFilter ref="A4:J23"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1551,7 +1651,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5263157894736842</v>
       </c>
     </row>
     <row r="6">
@@ -1561,10 +1661,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.4210526315789473</v>
       </c>
     </row>
     <row r="7">
@@ -1574,10 +1674,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -652,22 +652,22 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, molestation, abuse</t>
+          <t>assault, attack, molestation</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, permission</t>
+          <t>consent, permission, agreement</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating a rape case.</t>
+          <t>The police are investigating the rape case.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>crime</t>
+          <t>Crime</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or approach</t>
+          <t>to change direction or course of action</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>remain, stay</t>
+          <t>remain, stay, continue</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>The company needs to pivot its strategy to stay competitive.</t>
+          <t>The company will pivot its strategy to focus on renewable energy.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly</t>
+          <t>sustainable, eco-friendly, green</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, finite</t>
+          <t>non-renewable, finite, limited</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -785,39 +785,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>a score of 50 in a game or sport</t>
+          <t>the act of promoting a product or service</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>score, points</t>
+          <t>marketing, promotion, publicity</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>zero, loss</t>
+          <t>hiding, concealing, suppressing</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The team scored 50 runs in the fifties.</t>
+          <t>The company is investing heavily in advertising.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -827,47 +827,47 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>goods or products that are bought and sold</t>
+          <t>having too much at the top</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>goods, merchandise</t>
+          <t>unbalanced, uneven, disproportionate</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>services, intangible</t>
+          <t>balanced, even, proportionate</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The price of commodities has increased significantly.</t>
+          <t>The economy is top-heavy with too much debt.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>economics</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -877,47 +877,47 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>বেশি ব্যয়বহুল</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>more expensive</t>
+          <t>goods or products that can be bought and sold</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>costly, pricey</t>
+          <t>goods, merchandise, products</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>cheaper, affordable</t>
+          <t>services, intangibles, non-material</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The new phone is dearer than the old one.</t>
+          <t>The price of commodities is fluctuating wildly.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>dearer</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>adjective</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>বেশি মূল্যবান</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>the middle or most important part of something</t>
+          <t>more expensive</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>middle, center</t>
+          <t>costlier, pricier, more expensive</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>edge, periphery</t>
+          <t>cheaper, less expensive, less costly</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The city is located at the centre of the country.</t>
+          <t>The new smartphone is dearer than the old one.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,39 +985,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>the number 50</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle, conflict</t>
+          <t>fifty, fifty, fifty</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The two teams are engaged in a fierce battle.</t>
+          <t>The team scored 50 runs in the fifties.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>warm-up</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>গরমাগার</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>an exercise or activity to prepare for a competition</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>existence, life</t>
+          <t>practice, rehearsal, preparation</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>death, extinction</t>
+          <t>cool-down, relaxation, leisure</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament is uncertain.</t>
+          <t>The team had a warm-up session before the match.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1092,32 +1092,32 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>the expression or application of human creative skill and imagination</t>
+          <t>the middle or central part of something</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>craft, skill</t>
+          <t>middle, center, midpoint</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>science, technology</t>
+          <t>edge, boundary, periphery</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The artist is known for her beautiful paintings.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1142,32 +1142,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>something that is learned or taught</t>
+          <t>a platform or area for performance or display</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>knowledge, wisdom</t>
+          <t>platform, area, space</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>ignorance, foolishness</t>
+          <t>background, setting, context</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The teacher gave a lesson on history.</t>
+          <t>The actor took the stage to deliver his monologue.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>having too much at the top and not enough at the bottom</t>
+          <t>a fight or struggle between two or more people or groups</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>unbalanced, uneven</t>
+          <t>fight, struggle, conflict</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>balanced, stable</t>
+          <t>peace, harmony, agreement</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure is a major concern.</t>
+          <t>The team is preparing for the battle against their rivals.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>boon</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1235,344 +1235,44 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>বর</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>a benefit or advantage</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>advantage, benefit</t>
+          <t>existence, life, livelihood</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>disadvantage, loss</t>
+          <t>death, extinction, demise</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The new policy is a boon for the environment.</t>
+          <t>The team is fighting for survival in the league.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>society</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>পরিবারের জীবিকার্জক</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>to succeed or achieve something</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>succeed, achieve</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>lose, fail</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>The team won the match.</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>warm-up</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>গরমাগার</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>an activity or exercise done to prepare for something</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>exercise, preparation</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>relaxation, leisure</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>The team did a warm-up before the game.</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>centre</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>কেন্দ্র</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>the middle or most important part of something</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>middle, center</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>edge, periphery</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>The city is located at the centre of the country.</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>geography</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>stage</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>পর্যায়</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>a place or situation where something happens or is performed</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>place, location</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>absence, void</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>The play is being performed on stage.</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>arts</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>takes</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>গ্রহণ করা</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>to accept or receive something</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>accept, receive</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>reject, refuse</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>The team takes the lead in the tournament.</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Copa</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>বিশপ-সংক্রান্ত</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>a trophy or championship in football</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>trophy, championship</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>defeat, loss</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>The team won the Copa America.</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>sports</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J23"/>
+  <autoFilter ref="A4:J17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1648,10 +1348,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -1661,10 +1361,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="7">
@@ -1674,10 +1374,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -12,7 +12,7 @@
     <sheet name="BCS &amp; Bank Practice Set" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Star Vocabulary'!$A$4:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -652,17 +652,17 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, attack, molestation</t>
+          <t>assault, molestation, coercion</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, permission, agreement</t>
+          <t>consent, agreement</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating the rape case.</t>
+          <t>The police are investigating a case of rape.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>to change direction or course of action</t>
+          <t>to change direction or focus</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, change, alter</t>
+          <t>shift, alter, redirect</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>remain, stay, continue</t>
+          <t>stay, remain, continue</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>The company will pivot its strategy to focus on renewable energy.</t>
+          <t>The company needs to pivot its strategy to stay competitive.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -785,39 +785,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>উৎপাদনশীল</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>the act of promoting a product or service</t>
+          <t>goods or products that are widely available and traded</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>marketing, promotion, publicity</t>
+          <t>goods, products, merchandise</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>hiding, concealing, suppressing</t>
+          <t>services, intangibles, non-tradable</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The company is investing heavily in advertising.</t>
+          <t>The price of commodities is affected by global demand and supply.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Economy</t>
         </is>
       </c>
     </row>
@@ -827,47 +827,47 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>top-heavy</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>মাথাভারী</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>having too much at the top</t>
+          <t>a decade of the 20th century</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, uneven, disproportionate</t>
+          <t>fifties, 50s, 1950s</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>balanced, even, proportionate</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The economy is top-heavy with too much debt.</t>
+          <t>The fifties were a time of great social change.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -892,32 +892,32 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>পণ্য</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>goods or products that can be bought and sold</t>
+          <t>a central or middle point</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>goods, merchandise, products</t>
+          <t>center, middle, core</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles, non-material</t>
+          <t>periphery, edge, outer</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities is fluctuating wildly.</t>
+          <t>The city's centre is a popular tourist destination.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>dearer</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>noun</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>বেশি মূল্যবান</t>
+          <t>পর্যায়</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>more expensive</t>
+          <t>a platform or area for performance or display</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>costlier, pricier, more expensive</t>
+          <t>platform, arena, scene</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>cheaper, less expensive, less costly</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The new smartphone is dearer than the old one.</t>
+          <t>The actor took to the stage to deliver his monologue.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,34 +985,34 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>the number 50</t>
+          <t>a fight or struggle, especially a violent one</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>fifty, fifty, fifty</t>
+          <t>fight, struggle, combat</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>peace, harmony, cooperation</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The team scored 50 runs in the fifties.</t>
+          <t>The two teams are engaged in a fierce battle for the championship.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>warm-up</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1035,39 +1035,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>গরমাগার</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>an exercise or activity to prepare for a competition</t>
+          <t>the state of continuing to exist or live</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>practice, rehearsal, preparation</t>
+          <t>existence, life, persistence</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>cool-down, relaxation, leisure</t>
+          <t>extinction, death, demise</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team had a warm-up session before the match.</t>
+          <t>The team's survival in the tournament depends on their next game.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1085,39 +1085,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>the middle or central part of something</t>
+          <t>formal accusations or complaints</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>middle, center, midpoint</t>
+          <t>accusations, complaints, allegations</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>edge, boundary, periphery</t>
+          <t>acquittals, pardons, exoneration</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The city is located at the centre of the country.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>Law</t>
         </is>
       </c>
     </row>
@@ -1127,47 +1127,47 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>আকৃতি</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>a platform or area for performance or display</t>
+          <t>to be formally accused or charged</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>platform, area, space</t>
+          <t>accused, charged, indicted</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>background, setting, context</t>
+          <t>exonerated, acquitted, pardoned</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The actor took the stage to deliver his monologue.</t>
+          <t>The defendant was framed for the crime.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>Law</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>advertisement</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>বিজ্ঞাপন</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle between two or more people or groups</t>
+          <t>a public notice or announcement</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle, conflict</t>
+          <t>announcement, notice, advertisement</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony, agreement</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The team is preparing for the battle against their rivals.</t>
+          <t>The company placed an advertisement in the newspaper.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1235,44 +1235,294 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>শিল্প</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>the expression or application of human creative skill and imagination</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>craft, skill, technique</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>The artist's use of color was a work of art.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>বাঙালি</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>relating to or characteristic of Bangladesh or the Bengali people</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Bangladeshi, Bengalese</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>The Bengali language is spoken by millions of people.</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>উদ্বর্তন</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>the state of continuing to exist or live</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>existence, life, livelihood</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>death, extinction, demise</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>The team is fighting for survival in the league.</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Sports</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>বিজ্ঞাপন</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>the promotion of a product or service through various media</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>marketing, promotion, publicity</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>The company's advertising campaign was a huge success.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>booms</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>গম্ভীর গর্জন</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>to experience a sudden and rapid increase in growth or activity</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>grow, expand, flourish</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>decline, shrink, contract</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>The economy is booming, with many new businesses opening.</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>top-heavy</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>মাথাভারী</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>having too much weight or emphasis at the top</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>unbalanced, uneven, disproportionate</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>balanced, even, proportional</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>The company's top-heavy structure made it difficult to manage.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>শিক্ষা</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>a piece of advice or a moral teaching</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>advice, guidance, instruction</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>The teacher gave the students a lesson on responsibility.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Education</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J17"/>
+  <autoFilter ref="A4:J22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1348,10 +1598,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -1361,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1374,10 +1624,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="8">

--- a/data/Vocabulary_Bank.xlsx
+++ b/data/Vocabulary_Bank.xlsx
@@ -652,22 +652,22 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>assault, molestation, coercion</t>
+          <t>assault, molestation, violation</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>consent, agreement</t>
+          <t>consent, permission</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>The police are investigating a case of rape.</t>
+          <t>The police are investigating the rape of a young woman.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Crime</t>
+          <t>crime</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>shift, alter, redirect</t>
+          <t>shift, turn, change</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>stay, remain, continue</t>
+          <t>remain, stay</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sustainable, eco-friendly, green</t>
+          <t>sustainable, eco-friendly</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>non-renewable, finite, limited</t>
+          <t>non-renewable, finite</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>energy</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -785,39 +785,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>উৎপাদনশীল</t>
+          <t>শিল্প</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>goods or products that are widely available and traded</t>
+          <t>the expression or application of human creative skill and imagination</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>goods, products, merchandise</t>
+          <t>craft, skill</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>services, intangibles, non-tradable</t>
+          <t>science, technology</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>The price of commodities is affected by global demand and supply.</t>
+          <t>She is a talented artist.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>culture</t>
         </is>
       </c>
     </row>
@@ -827,47 +827,47 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>fifties</t>
+          <t>top-heavy</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>adjective</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>পঞ্চাশ</t>
+          <t>মাথাভারী</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>a decade of the 20th century</t>
+          <t>having too much weight or importance at the top</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>fifties, 50s, 1950s</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced, stable</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>The fifties were a time of great social change.</t>
+          <t>The economy is top-heavy and needs to be reformed.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -892,32 +892,32 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>কেন্দ্র</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>a central or middle point</t>
+          <t>goods or materials that can be bought or sold</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>center, middle, core</t>
+          <t>goods, merchandise</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>periphery, edge, outer</t>
+          <t>services, intangibles</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>The city's centre is a popular tourist destination.</t>
+          <t>The price of commodities is fluctuating.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>পর্যায়</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>a platform or area for performance or display</t>
+          <t>a decade of years</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>platform, arena, scene</t>
+          <t>fifties, fifty</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>sixties, sixty</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>The actor took to the stage to deliver his monologue.</t>
+          <t>He scored a century in his fifties.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>numbers</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>centre</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -985,39 +985,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>যুদ্ধ</t>
+          <t>কেন্দ্র</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>a fight or struggle, especially a violent one</t>
+          <t>a middle point or position</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>fight, struggle, combat</t>
+          <t>center, middle</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>peace, harmony, cooperation</t>
+          <t>periphery, edge</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>The two teams are engaged in a fierce battle for the championship.</t>
+          <t>The city is located at the centre of the country.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>location</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>survival</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1035,39 +1035,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>উদ্বর্তন</t>
+          <t>যুদ্ধ</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>the state of continuing to exist or live</t>
+          <t>a fight or struggle</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>existence, life, persistence</t>
+          <t>fight, struggle</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>extinction, death, demise</t>
+          <t>peace, harmony</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The team's survival in the tournament depends on their next game.</t>
+          <t>The two teams are battling for the championship.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>sports</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>charges</t>
+          <t>survival</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1092,32 +1092,32 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>অভিযোগ</t>
+          <t>উদ্বর্তন</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>formal accusations or complaints</t>
+          <t>the state of continuing to exist</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>accusations, complaints, allegations</t>
+          <t>existence, life</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>acquittals, pardons, exoneration</t>
+          <t>death, extinction</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>The police have filed charges against the suspect.</t>
+          <t>The team is fighting for survival in the league.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -1127,47 +1127,47 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>framed</t>
+          <t>charges</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>আকৃতি</t>
+          <t>অভিযোগ</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>to be formally accused or charged</t>
+          <t>official accusations of wrongdoing</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>accused, charged, indicted</t>
+          <t>accusations, allegations</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>exonerated, acquitted, pardoned</t>
+          <t>clearance, exoneration</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The defendant was framed for the crime.</t>
+          <t>The police have filed charges against the suspect.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>advertisement</t>
+          <t>framed</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>বিজ্ঞাপন</t>
+          <t>ফ্রেম করা</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>a public notice or announcement</t>
+          <t>to put something in a frame or to accuse someone of a crime</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>announcement, notice, advertisement</t>
+          <t>accused, charged</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>cleared, exonerated</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>The company placed an advertisement in the newspaper.</t>
+          <t>The suspect has been framed for the crime.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>law</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>must</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>noun</t>
+          <t>verb</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>শিল্প</t>
+          <t>অবশ্যই</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>the expression or application of human creative skill and imagination</t>
+          <t>a necessity or requirement</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>craft, skill, technique</t>
+          <t>need, require</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>optional, voluntary</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>The artist's use of color was a work of art.</t>
+          <t>You must attend the meeting.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Arts</t>
+          <t>language</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>boon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>adjective</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>বাঙালি</t>
+          <t>বর</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>relating to or characteristic of Bangladesh or the Bengali people</t>
+          <t>a benefit or advantage</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Bangladeshi, Bengalese</t>
+          <t>benefit, advantage</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>disadvantage, harm</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>The Bengali language is spoken by millions of people.</t>
+          <t>The new policy is a boon for the economy.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>advertisement</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1347,27 +1347,27 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>the promotion of a product or service through various media</t>
+          <t>a public notice or announcement</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>marketing, promotion, publicity</t>
+          <t>announcement, notice</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>secret, hidden</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>The company's advertising campaign was a huge success.</t>
+          <t>The company is running an advertisement on TV.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1377,47 +1377,47 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>booms</t>
+          <t>fifties</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>verb</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
+          <t>noun</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>গম্ভীর গর্জন</t>
+          <t>পঞ্চাশ</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>to experience a sudden and rapid increase in growth or activity</t>
+          <t>a decade of years</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>grow, expand, flourish</t>
+          <t>fifties, fifty</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>decline, shrink, contract</t>
+          <t>sixties, sixty</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>The economy is booming, with many new businesses opening.</t>
+          <t>He scored a century in his fifties.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>numbers</t>
         </is>
       </c>
     </row>
@@ -1435,9 +1435,9 @@
           <t>adjective</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Advanced</t>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>having too much weight or emphasis at the top</t>
+          <t>having too much weight or importance at the top</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>unbalanced, uneven, disproportionate</t>
+          <t>unbalanced, uneven</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>balanced, even, proportional</t>
+          <t>balanced, stable</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>The company's top-heavy structure made it difficult to manage.</t>
+          <t>The economy is top-heavy and needs to be reformed.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1485,39 +1485,39 @@
           <t>noun</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Basic</t>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>শিক্ষা</t>
+          <t>পণ্য</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>a piece of advice or a moral teaching</t>
+          <t>goods or materials that can be bought or sold</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>advice, guidance, instruction</t>
+          <t>goods, merchandise</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>services, intangibles</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>The teacher gave the students a lesson on responsibility.</t>
+          <t>The price of commodities is fluctuating.</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>economy</t>
         </is>
       </c>
     </row>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.5</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="7">
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="8">
